--- a/上架准备工作按周排期_2026-08_2027-02.xlsx
+++ b/上架准备工作按周排期_2026-08_2027-02.xlsx
@@ -47,7 +47,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -81,7 +81,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00BDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D2E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -111,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -144,7 +154,13 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -512,10 +528,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="120" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -565,96 +581,120 @@
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>反推提前量</t>
+          <t>反推提前量与选款错峰</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>妈妈装/婚纱: 上架前第5周启动选款; 常规品类: 前第4周; 小批次(≤20款): 前第3周合并选款+打分(或直接定款), 可再压缩。</t>
+          <t>妈妈装/婚纱/舞会裙: 上架前第5周启动选款; 晚礼服/伴娘裙: 前第4周; 小批次(≤20款): 前第3周合并选款+打分。经错峰后每周组内选款不超过2个大批次。</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>上架节奏</t>
+          <t>已定款库存</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>每周上新: 月量≥40款的品类按月内各周均摊; 21-39款分2周; ≤20款集中1周上架(各品类错开周次, 平衡周上架总量)。</t>
+          <t>CD/JBD 现有50款已定款: 覆盖 CD 9月批(20款) + JBD 10月批(30款), 这两批跳过选款/打分/定款, 直接生成SPU+作图。如实际分配不同可在表中调整。</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>选款产能</t>
+          <t>婚纱来图定制</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>选款池按定款量的1.5倍备选(可调); 人均选款产能: 大批次(≥40款)一人每周40款, 小批次一人每周20款。详见"产能与作图拆解"表。</t>
+          <t>婚纱每月约20款新品来自来图定制, 无需选款/打分/定款。9-11月婚纱拆为"选款批+来图定制批"两行; 12月-2月计划量(各10款)全部由定制覆盖, 无需选款。8月婚纱需紧急定款量由50款降为30款。</t>
         </is>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>直接定款(灵活机制)</t>
+          <t>直接定款候选</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>若某周选款/打分排不开, 小批次品类(CD/FG/JBD/Prom及低量月份的WD)可由负责人直接定款, 跳过组内打分, 整体可压缩1-2周。甘特为标准节奏, 实际执行允许±1周浮动, 但作图完成时间不得晚于对应上架周的前一个周五。</t>
+          <t>甘特表"直接定款建议"列(红色)标注了选款/定款周与其他大批次选款撞期的批次(FG各批、JBD 12月批、WD 8月批), 执行时若当周人力排不开, 由负责人直接定款, 整体可再压缩1周。</t>
         </is>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>春节安排</t>
+          <t>上架节奏</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>假设 2027/2/5-2/18 放假14天(以公司通知为准), 2/8周与2/15周不排任何工作。2月120款全部于 1/29(节前)完成作图, 分 2/1周(65款)与 2/22周(55款)两次上架。</t>
+          <t>每周上新: 月量≥40款的品类按月内各周均摊; 21-39款分2周; ≤20款集中1周上架(各品类错开周次, 平衡周上架总量)。</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>选款产能</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>选款池按定款量的1.5倍备选(可调); 人均选款产能: 大批次(≥40款)一人每周40款, 小批次一人每周20款。详见"产能与作图拆解"表。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>春节安排</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>假设 2027/2/5-2/18 放假14天(以公司通知为准), 2/8周与2/15周不排任何工作。2月120款全部于 1/29(节前)完成作图, 分 2/1周(65款)与 2/22周(55款)两次上架。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
           <t>2027-03 批次提示</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>受春节影响, 3月批次(量待定)中妈妈装/婚纱需提前: 1/18-1/29 完成选款打分定款, 节前完成SPU并启动作图, 节后 2/22周 收尾作图, 3月第1周正常上架; 常规品类节后 2/22周 立即选款(或直接定款)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="42" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>受春节影响, 3月批次(量待定)中妈妈装需提前: 1/18-1/29 完成选款打分定款, 节前完成SPU并启动作图, 节后 2/22周 收尾作图, 3月第1周正常上架; 常规品类节后 2/22周 立即选款(或直接定款); 婚纱可优先用来图定制款过渡。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>8月追赶(当前进度)</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>BD: 选款打分已完成→本周定款; ED: 已定款→本周SPU+作图; MBD: 作图中→8/10周起滚动上架; WD: 未启动→高风险, 建议本周直接定款并压缩作图, 8/24周起上架, 必要时部分顺延至9月第1周。8月上架量后置明显(8/24、8/31两周合计145款), 属追赶期特殊情况。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>BD: 选款打分已完成→本周定款; ED: 已定款→本周SPU+作图; MBD: 作图中→8/10周起滚动上架; WD: 未启动→本周直接定款30款(来图定制另覆盖20款), 8/24周起上架, 必要时部分顺延至9月第1周。8月上架量后置明显(8/24、8/31两周合计145款), 属追赶期特殊情况。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>图例</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>选款=浅蓝, 打分=黄色, 定款=橙色, 生成SPU=浅紫, 作图=蓝紫, 上架=绿色, 春节假期=灰色。</t>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>选款=浅蓝, 打分=黄色, 定款=橙色, 生成SPU=浅紫, 作图=蓝紫, 上架=绿色, 春节假期=灰色, 直接定款候选=红色。</t>
         </is>
       </c>
     </row>
@@ -1409,10 +1449,10 @@
       <c r="B4" s="5" t="inlineStr"/>
       <c r="C4" s="5" t="inlineStr"/>
       <c r="D4" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F4" s="7" t="n">
         <v>13</v>
@@ -1459,10 +1499,10 @@
       </c>
       <c r="U4" s="5" t="inlineStr"/>
       <c r="V4" s="5" t="inlineStr"/>
-      <c r="W4" s="5" t="inlineStr"/>
-      <c r="X4" s="7" t="n">
+      <c r="W4" s="7" t="n">
         <v>10</v>
       </c>
+      <c r="X4" s="5" t="inlineStr"/>
       <c r="Y4" s="5" t="inlineStr"/>
       <c r="Z4" s="5" t="inlineStr"/>
       <c r="AA4" s="7" t="n">
@@ -1656,10 +1696,10 @@
       <c r="T7" s="5" t="inlineStr"/>
       <c r="U7" s="5" t="inlineStr"/>
       <c r="V7" s="5" t="inlineStr"/>
-      <c r="W7" s="7" t="n">
+      <c r="W7" s="5" t="inlineStr"/>
+      <c r="X7" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="X7" s="5" t="inlineStr"/>
       <c r="Y7" s="7" t="n">
         <v>15</v>
       </c>
@@ -1781,10 +1821,10 @@
         <v>35</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>68</v>
@@ -1838,10 +1878,10 @@
         <v>72</v>
       </c>
       <c r="W10" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="X10" s="6" t="n">
         <v>65</v>
-      </c>
-      <c r="X10" s="6" t="n">
-        <v>60</v>
       </c>
       <c r="Y10" s="6" t="n">
         <v>65</v>
@@ -1880,10 +1920,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI44"/>
+  <dimension ref="A1:AJ48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="10.5" customWidth="1" min="4" max="4"/>
@@ -1917,7 +1957,8 @@
     <col width="10.5" customWidth="1" min="32" max="32"/>
     <col width="10.5" customWidth="1" min="33" max="33"/>
     <col width="10.5" customWidth="1" min="34" max="34"/>
-    <col width="46" customWidth="1" min="35" max="35"/>
+    <col width="38" customWidth="1" min="35" max="35"/>
+    <col width="46" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2123,6 +2164,11 @@
         </is>
       </c>
       <c r="AI1" s="4" t="inlineStr">
+        <is>
+          <t>直接定款建议</t>
+        </is>
+      </c>
+      <c r="AJ1" s="4" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -2201,7 +2247,8 @@
       </c>
       <c r="AG2" s="5" t="inlineStr"/>
       <c r="AH2" s="5" t="inlineStr"/>
-      <c r="AI2" s="3" t="inlineStr">
+      <c r="AI2" s="3" t="inlineStr"/>
+      <c r="AJ2" s="3" t="inlineStr">
         <is>
           <t>已在作图环节, 边作图边滚动上架</t>
         </is>
@@ -2280,7 +2327,8 @@
       </c>
       <c r="AG3" s="5" t="inlineStr"/>
       <c r="AH3" s="5" t="inlineStr"/>
-      <c r="AI3" s="3" t="inlineStr">
+      <c r="AI3" s="3" t="inlineStr"/>
+      <c r="AJ3" s="3" t="inlineStr">
         <is>
           <t>定款已完成, 本周生成SPU并启动作图</t>
         </is>
@@ -2289,7 +2337,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>婚纱 Bride</t>
+          <t>婚纱 Bride(选款)</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -2298,7 +2346,7 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
@@ -2315,14 +2363,14 @@
           <t>作图</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>作图+上架15</t>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>作图</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>上架35</t>
+          <t>上架30</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr"/>
@@ -2359,16 +2407,21 @@
       </c>
       <c r="AG4" s="5" t="inlineStr"/>
       <c r="AH4" s="5" t="inlineStr"/>
-      <c r="AI4" s="3" t="inlineStr">
-        <is>
-          <t>尚未启动, 高风险: 建议本周直接定款(跳过打分), 作图压缩; 如仍延期可将部分顺延至9/7周</t>
+      <c r="AI4" s="12" t="inlineStr">
+        <is>
+          <t>追赶批次, 建议直接定款</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr">
+        <is>
+          <t>尚未启动, 本周直接定款(跳过打分); 来图定制覆盖20款后仅需定30款, 如仍延期可部分顺延至9/7周</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>伴娘裙 Bridesmaid</t>
+          <t>婚纱 Bride(来图定制)</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -2377,13 +2430,9 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>定款</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="D5" s="5" t="inlineStr"/>
       <c r="E5" s="10" t="inlineStr">
         <is>
           <t>SPU+作图</t>
@@ -2399,11 +2448,7 @@
           <t>上架20</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>上架20</t>
-        </is>
-      </c>
+      <c r="H5" s="5" t="inlineStr"/>
       <c r="I5" s="5" t="inlineStr"/>
       <c r="J5" s="5" t="inlineStr"/>
       <c r="K5" s="5" t="inlineStr"/>
@@ -2438,71 +2483,56 @@
       </c>
       <c r="AG5" s="5" t="inlineStr"/>
       <c r="AH5" s="5" t="inlineStr"/>
-      <c r="AI5" s="3" t="inlineStr">
-        <is>
-          <t>选款打分已完成, 本周内定款</t>
+      <c r="AI5" s="3" t="inlineStr"/>
+      <c r="AJ5" s="3" t="inlineStr">
+        <is>
+          <t>来图定制来源, 无需选款打分定款</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>妈妈装 Mother of the Bride</t>
+          <t>伴娘裙 Bridesmaid</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>2026-09 批</t>
+          <t>2026-08 批</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>选款</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>打分+定款</t>
+        <v>40</v>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>定款</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>SPU+作图</t>
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>SPU+作图</t>
-        </is>
-      </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
           <t>作图</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>作图</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>上架20</t>
         </is>
       </c>
-      <c r="J6" s="7" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>上架20</t>
         </is>
       </c>
-      <c r="K6" s="7" t="inlineStr">
-        <is>
-          <t>上架20</t>
-        </is>
-      </c>
-      <c r="L6" s="7" t="inlineStr">
-        <is>
-          <t>上架20</t>
-        </is>
-      </c>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
       <c r="M6" s="5" t="inlineStr"/>
       <c r="N6" s="5" t="inlineStr"/>
       <c r="O6" s="5" t="inlineStr"/>
@@ -2533,16 +2563,17 @@
       </c>
       <c r="AG6" s="5" t="inlineStr"/>
       <c r="AH6" s="5" t="inlineStr"/>
-      <c r="AI6" s="3" t="inlineStr">
-        <is>
-          <t>复杂品类(60%+单个作图), 作图排3周</t>
+      <c r="AI6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr">
+        <is>
+          <t>选款打分已完成, 本周内定款</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>晚礼服 Evening</t>
+          <t>妈妈装 Mother of the Bride</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -2551,22 +2582,26 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="12" t="inlineStr">
+        <v>80</v>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>选款</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>打分+定款</t>
         </is>
       </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>SPU+作图</t>
+        </is>
+      </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>SPU+作图</t>
+          <t>作图</t>
         </is>
       </c>
       <c r="H7" s="10" t="inlineStr">
@@ -2576,22 +2611,22 @@
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>上架10</t>
+          <t>上架20</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>上架10</t>
+          <t>上架20</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>上架10</t>
+          <t>上架20</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>上架10</t>
+          <t>上架20</t>
         </is>
       </c>
       <c r="M7" s="5" t="inlineStr"/>
@@ -2625,11 +2660,16 @@
       <c r="AG7" s="5" t="inlineStr"/>
       <c r="AH7" s="5" t="inlineStr"/>
       <c r="AI7" s="3" t="inlineStr"/>
+      <c r="AJ7" s="3" t="inlineStr">
+        <is>
+          <t>复杂品类(60%+单个作图), 作图排3周</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>婚纱 Bride</t>
+          <t>晚礼服 Evening</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -2638,51 +2678,47 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
+        <v>40</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>选款</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>打分+定款</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>SPU+作图</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>作图</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>作图</t>
-        </is>
-      </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>上架13</t>
+          <t>上架10</t>
         </is>
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>上架13</t>
+          <t>上架10</t>
         </is>
       </c>
       <c r="K8" s="7" t="inlineStr">
         <is>
-          <t>上架12</t>
+          <t>上架10</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
-          <t>上架12</t>
+          <t>上架10</t>
         </is>
       </c>
       <c r="M8" s="5" t="inlineStr"/>
@@ -2715,16 +2751,13 @@
       </c>
       <c r="AG8" s="5" t="inlineStr"/>
       <c r="AH8" s="5" t="inlineStr"/>
-      <c r="AI8" s="3" t="inlineStr">
-        <is>
-          <t>复杂品类(60%+单个作图), 作图排3周</t>
-        </is>
-      </c>
+      <c r="AI8" s="3" t="inlineStr"/>
+      <c r="AJ8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>伴娘裙 Bridesmaid</t>
+          <t>婚纱 Bride(选款)</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -2733,22 +2766,26 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="12" t="inlineStr">
+        <v>30</v>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>选款</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>打分+定款</t>
         </is>
       </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>SPU+作图</t>
+        </is>
+      </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>SPU+作图</t>
+          <t>作图</t>
         </is>
       </c>
       <c r="H9" s="10" t="inlineStr">
@@ -2758,22 +2795,22 @@
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>上架10</t>
+          <t>上架8</t>
         </is>
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>上架10</t>
+          <t>上架8</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>上架10</t>
+          <t>上架7</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>上架10</t>
+          <t>上架7</t>
         </is>
       </c>
       <c r="M9" s="5" t="inlineStr"/>
@@ -2807,11 +2844,16 @@
       <c r="AG9" s="5" t="inlineStr"/>
       <c r="AH9" s="5" t="inlineStr"/>
       <c r="AI9" s="3" t="inlineStr"/>
+      <c r="AJ9" s="3" t="inlineStr">
+        <is>
+          <t>复杂品类, 作图排3周; 仅需定款计划量减去定制20款后的部分</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>鸡尾酒裙 Cocktail</t>
+          <t>婚纱 Bride(来图定制)</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -2825,28 +2867,36 @@
       <c r="D10" s="5" t="inlineStr"/>
       <c r="E10" s="5" t="inlineStr"/>
       <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="11" t="inlineStr">
-        <is>
-          <t>选款+打分+定款</t>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>SPU+作图</t>
         </is>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>SPU+作图</t>
-        </is>
-      </c>
-      <c r="I10" s="10" t="inlineStr">
-        <is>
           <t>作图</t>
         </is>
       </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>上架5</t>
+        </is>
+      </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>上架20</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr"/>
-      <c r="L10" s="5" t="inlineStr"/>
+          <t>上架5</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>上架5</t>
+        </is>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>上架5</t>
+        </is>
+      </c>
       <c r="M10" s="5" t="inlineStr"/>
       <c r="N10" s="5" t="inlineStr"/>
       <c r="O10" s="5" t="inlineStr"/>
@@ -2877,16 +2927,17 @@
       </c>
       <c r="AG10" s="5" t="inlineStr"/>
       <c r="AH10" s="5" t="inlineStr"/>
-      <c r="AI10" s="3" t="inlineStr">
-        <is>
-          <t>小批次: 选款打分同周合并, 可走直接定款再压缩1周</t>
+      <c r="AI10" s="3" t="inlineStr"/>
+      <c r="AJ10" s="3" t="inlineStr">
+        <is>
+          <t>来图定制来源(月供约20款), 无需选款打分定款</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>花童裙 Flower Girl</t>
+          <t>伴娘裙 Bridesmaid</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -2895,10 +2946,10 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>选款</t>
         </is>
@@ -2920,16 +2971,24 @@
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>上架15</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr"/>
+          <t>上架10</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>上架10</t>
+        </is>
+      </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>上架15</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr"/>
+          <t>上架10</t>
+        </is>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>上架10</t>
+        </is>
+      </c>
       <c r="M11" s="5" t="inlineStr"/>
       <c r="N11" s="5" t="inlineStr"/>
       <c r="O11" s="5" t="inlineStr"/>
@@ -2961,70 +3020,47 @@
       <c r="AG11" s="5" t="inlineStr"/>
       <c r="AH11" s="5" t="inlineStr"/>
       <c r="AI11" s="3" t="inlineStr"/>
+      <c r="AJ11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>妈妈装 Mother of the Bride</t>
+          <t>鸡尾酒裙 Cocktail</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>2026-10 批</t>
+          <t>2026-09 批</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="D12" s="5" t="inlineStr"/>
       <c r="E12" s="5" t="inlineStr"/>
       <c r="F12" s="5" t="inlineStr"/>
       <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="12" t="inlineStr">
-        <is>
-          <t>选款</t>
-        </is>
-      </c>
-      <c r="I12" s="11" t="inlineStr">
-        <is>
-          <t>打分+定款</t>
-        </is>
-      </c>
-      <c r="J12" s="10" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>SPU+作图</t>
         </is>
       </c>
-      <c r="K12" s="10" t="inlineStr">
+      <c r="I12" s="10" t="inlineStr">
         <is>
           <t>作图</t>
         </is>
       </c>
-      <c r="L12" s="10" t="inlineStr">
-        <is>
-          <t>作图</t>
-        </is>
-      </c>
-      <c r="M12" s="7" t="inlineStr">
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>上架20</t>
         </is>
       </c>
-      <c r="N12" s="7" t="inlineStr">
-        <is>
-          <t>上架20</t>
-        </is>
-      </c>
-      <c r="O12" s="7" t="inlineStr">
-        <is>
-          <t>上架20</t>
-        </is>
-      </c>
-      <c r="P12" s="7" t="inlineStr">
-        <is>
-          <t>上架20</t>
-        </is>
-      </c>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="5" t="inlineStr"/>
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="5" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr"/>
       <c r="Q12" s="5" t="inlineStr"/>
       <c r="R12" s="5" t="inlineStr"/>
       <c r="S12" s="5" t="inlineStr"/>
@@ -3051,71 +3087,64 @@
       </c>
       <c r="AG12" s="5" t="inlineStr"/>
       <c r="AH12" s="5" t="inlineStr"/>
-      <c r="AI12" s="3" t="inlineStr">
-        <is>
-          <t>复杂品类(60%+单个作图), 作图排3周</t>
+      <c r="AI12" s="3" t="inlineStr"/>
+      <c r="AJ12" s="3" t="inlineStr">
+        <is>
+          <t>已定款库存覆盖(50款库存之20款), 直接SPU+作图</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>晚礼服 Evening</t>
+          <t>花童裙 Flower Girl</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-10 批</t>
+          <t>2026-09 批</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5" t="inlineStr"/>
-      <c r="F13" s="5" t="inlineStr"/>
-      <c r="G13" s="5" t="inlineStr"/>
-      <c r="H13" s="5" t="inlineStr"/>
-      <c r="I13" s="12" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>选款</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>打分+定款</t>
         </is>
       </c>
-      <c r="K13" s="10" t="inlineStr">
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t>SPU+作图</t>
         </is>
       </c>
-      <c r="L13" s="10" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>作图</t>
         </is>
       </c>
-      <c r="M13" s="7" t="inlineStr">
-        <is>
-          <t>上架10</t>
-        </is>
-      </c>
-      <c r="N13" s="7" t="inlineStr">
-        <is>
-          <t>上架10</t>
-        </is>
-      </c>
-      <c r="O13" s="7" t="inlineStr">
-        <is>
-          <t>上架10</t>
-        </is>
-      </c>
-      <c r="P13" s="7" t="inlineStr">
-        <is>
-          <t>上架10</t>
-        </is>
-      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>上架15</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>上架15</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr"/>
       <c r="Q13" s="5" t="inlineStr"/>
       <c r="R13" s="5" t="inlineStr"/>
       <c r="S13" s="5" t="inlineStr"/>
@@ -3142,12 +3171,17 @@
       </c>
       <c r="AG13" s="5" t="inlineStr"/>
       <c r="AH13" s="5" t="inlineStr"/>
-      <c r="AI13" s="3" t="inlineStr"/>
+      <c r="AI13" s="12" t="inlineStr">
+        <is>
+          <t>选款周(8/10)与ED/BD 9月批撞期, 建议直接定款</t>
+        </is>
+      </c>
+      <c r="AJ13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>婚纱 Bride</t>
+          <t>妈妈装 Mother of the Bride</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -3156,13 +3190,13 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="D14" s="5" t="inlineStr"/>
       <c r="E14" s="5" t="inlineStr"/>
       <c r="F14" s="5" t="inlineStr"/>
       <c r="G14" s="5" t="inlineStr"/>
-      <c r="H14" s="12" t="inlineStr">
+      <c r="H14" s="13" t="inlineStr">
         <is>
           <t>选款</t>
         </is>
@@ -3189,22 +3223,22 @@
       </c>
       <c r="M14" s="7" t="inlineStr">
         <is>
-          <t>上架10</t>
+          <t>上架20</t>
         </is>
       </c>
       <c r="N14" s="7" t="inlineStr">
         <is>
-          <t>上架10</t>
+          <t>上架20</t>
         </is>
       </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>上架10</t>
+          <t>上架20</t>
         </is>
       </c>
       <c r="P14" s="7" t="inlineStr">
         <is>
-          <t>上架10</t>
+          <t>上架20</t>
         </is>
       </c>
       <c r="Q14" s="5" t="inlineStr"/>
@@ -3233,7 +3267,8 @@
       </c>
       <c r="AG14" s="5" t="inlineStr"/>
       <c r="AH14" s="5" t="inlineStr"/>
-      <c r="AI14" s="3" t="inlineStr">
+      <c r="AI14" s="3" t="inlineStr"/>
+      <c r="AJ14" s="3" t="inlineStr">
         <is>
           <t>复杂品类(60%+单个作图), 作图排3周</t>
         </is>
@@ -3242,7 +3277,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>伴娘裙 Bridesmaid</t>
+          <t>晚礼服 Evening</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -3258,7 +3293,7 @@
       <c r="F15" s="5" t="inlineStr"/>
       <c r="G15" s="5" t="inlineStr"/>
       <c r="H15" s="5" t="inlineStr"/>
-      <c r="I15" s="12" t="inlineStr">
+      <c r="I15" s="13" t="inlineStr">
         <is>
           <t>选款</t>
         </is>
@@ -3325,11 +3360,12 @@
       <c r="AG15" s="5" t="inlineStr"/>
       <c r="AH15" s="5" t="inlineStr"/>
       <c r="AI15" s="3" t="inlineStr"/>
+      <c r="AJ15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>鸡尾酒裙 Cocktail</t>
+          <t>婚纱 Bride(选款)</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -3338,37 +3374,57 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D16" s="5" t="inlineStr"/>
       <c r="E16" s="5" t="inlineStr"/>
       <c r="F16" s="5" t="inlineStr"/>
       <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="11" t="inlineStr">
-        <is>
-          <t>选款+打分+定款</t>
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <t>选款</t>
+        </is>
+      </c>
+      <c r="I16" s="11" t="inlineStr">
+        <is>
+          <t>打分+定款</t>
+        </is>
+      </c>
+      <c r="J16" s="10" t="inlineStr">
+        <is>
+          <t>SPU+作图</t>
+        </is>
+      </c>
+      <c r="K16" s="10" t="inlineStr">
+        <is>
+          <t>作图</t>
         </is>
       </c>
       <c r="L16" s="10" t="inlineStr">
         <is>
-          <t>SPU+作图</t>
-        </is>
-      </c>
-      <c r="M16" s="10" t="inlineStr">
-        <is>
           <t>作图</t>
         </is>
       </c>
+      <c r="M16" s="7" t="inlineStr">
+        <is>
+          <t>上架5</t>
+        </is>
+      </c>
       <c r="N16" s="7" t="inlineStr">
         <is>
-          <t>上架10</t>
-        </is>
-      </c>
-      <c r="O16" s="5" t="inlineStr"/>
-      <c r="P16" s="5" t="inlineStr"/>
+          <t>上架5</t>
+        </is>
+      </c>
+      <c r="O16" s="7" t="inlineStr">
+        <is>
+          <t>上架5</t>
+        </is>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>上架5</t>
+        </is>
+      </c>
       <c r="Q16" s="5" t="inlineStr"/>
       <c r="R16" s="5" t="inlineStr"/>
       <c r="S16" s="5" t="inlineStr"/>
@@ -3395,16 +3451,17 @@
       </c>
       <c r="AG16" s="5" t="inlineStr"/>
       <c r="AH16" s="5" t="inlineStr"/>
-      <c r="AI16" s="3" t="inlineStr">
-        <is>
-          <t>小批次: 选款打分同周合并, 可走直接定款再压缩1周</t>
+      <c r="AI16" s="3" t="inlineStr"/>
+      <c r="AJ16" s="3" t="inlineStr">
+        <is>
+          <t>复杂品类, 作图排3周; 仅需定款计划量减去定制20款后的部分</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>花童裙 Flower Girl</t>
+          <t>婚纱 Bride(来图定制)</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -3422,26 +3479,34 @@
       <c r="H17" s="5" t="inlineStr"/>
       <c r="I17" s="5" t="inlineStr"/>
       <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
-      <c r="L17" s="5" t="inlineStr"/>
-      <c r="M17" s="11" t="inlineStr">
-        <is>
-          <t>选款+打分+定款</t>
-        </is>
-      </c>
-      <c r="N17" s="10" t="inlineStr">
+      <c r="K17" s="10" t="inlineStr">
         <is>
           <t>SPU+作图</t>
         </is>
       </c>
-      <c r="O17" s="10" t="inlineStr">
+      <c r="L17" s="10" t="inlineStr">
         <is>
           <t>作图</t>
         </is>
       </c>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>上架5</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="inlineStr">
+        <is>
+          <t>上架5</t>
+        </is>
+      </c>
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t>上架5</t>
+        </is>
+      </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
-          <t>上架20</t>
+          <t>上架5</t>
         </is>
       </c>
       <c r="Q17" s="5" t="inlineStr"/>
@@ -3470,16 +3535,17 @@
       </c>
       <c r="AG17" s="5" t="inlineStr"/>
       <c r="AH17" s="5" t="inlineStr"/>
-      <c r="AI17" s="3" t="inlineStr">
-        <is>
-          <t>小批次: 选款打分同周合并, 可走直接定款再压缩1周</t>
+      <c r="AI17" s="3" t="inlineStr"/>
+      <c r="AJ17" s="3" t="inlineStr">
+        <is>
+          <t>来图定制来源(月供约20款), 无需选款打分定款</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>小伴娘裙 JBD</t>
+          <t>伴娘裙 Bridesmaid</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -3488,14 +3554,14 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="5" t="inlineStr"/>
       <c r="F18" s="5" t="inlineStr"/>
       <c r="G18" s="5" t="inlineStr"/>
       <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="12" t="inlineStr">
+      <c r="I18" s="13" t="inlineStr">
         <is>
           <t>选款</t>
         </is>
@@ -3517,16 +3583,24 @@
       </c>
       <c r="M18" s="7" t="inlineStr">
         <is>
-          <t>上架15</t>
-        </is>
-      </c>
-      <c r="N18" s="5" t="inlineStr"/>
+          <t>上架10</t>
+        </is>
+      </c>
+      <c r="N18" s="7" t="inlineStr">
+        <is>
+          <t>上架10</t>
+        </is>
+      </c>
       <c r="O18" s="7" t="inlineStr">
         <is>
-          <t>上架15</t>
-        </is>
-      </c>
-      <c r="P18" s="5" t="inlineStr"/>
+          <t>上架10</t>
+        </is>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>上架10</t>
+        </is>
+      </c>
       <c r="Q18" s="5" t="inlineStr"/>
       <c r="R18" s="5" t="inlineStr"/>
       <c r="S18" s="5" t="inlineStr"/>
@@ -3554,20 +3628,21 @@
       <c r="AG18" s="5" t="inlineStr"/>
       <c r="AH18" s="5" t="inlineStr"/>
       <c r="AI18" s="3" t="inlineStr"/>
+      <c r="AJ18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>妈妈装 Mother of the Bride</t>
+          <t>鸡尾酒裙 Cocktail</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>2026-11 批</t>
+          <t>2026-10 批</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="D19" s="5" t="inlineStr"/>
       <c r="E19" s="5" t="inlineStr"/>
@@ -3576,57 +3651,33 @@
       <c r="H19" s="5" t="inlineStr"/>
       <c r="I19" s="5" t="inlineStr"/>
       <c r="J19" s="5" t="inlineStr"/>
-      <c r="K19" s="5" t="inlineStr"/>
-      <c r="L19" s="12" t="inlineStr">
-        <is>
-          <t>选款</t>
-        </is>
-      </c>
-      <c r="M19" s="11" t="inlineStr">
-        <is>
-          <t>打分+定款</t>
-        </is>
-      </c>
-      <c r="N19" s="10" t="inlineStr">
+      <c r="K19" s="11" t="inlineStr">
+        <is>
+          <t>选款+打分+定款</t>
+        </is>
+      </c>
+      <c r="L19" s="10" t="inlineStr">
         <is>
           <t>SPU+作图</t>
         </is>
       </c>
-      <c r="O19" s="10" t="inlineStr">
+      <c r="M19" s="10" t="inlineStr">
         <is>
           <t>作图</t>
         </is>
       </c>
-      <c r="P19" s="10" t="inlineStr">
-        <is>
-          <t>作图</t>
-        </is>
-      </c>
-      <c r="Q19" s="7" t="inlineStr">
-        <is>
-          <t>上架20</t>
-        </is>
-      </c>
-      <c r="R19" s="7" t="inlineStr">
-        <is>
-          <t>上架20</t>
-        </is>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>上架20</t>
-        </is>
-      </c>
-      <c r="T19" s="7" t="inlineStr">
-        <is>
-          <t>上架20</t>
-        </is>
-      </c>
-      <c r="U19" s="7" t="inlineStr">
-        <is>
-          <t>上架20</t>
-        </is>
-      </c>
+      <c r="N19" s="7" t="inlineStr">
+        <is>
+          <t>上架10</t>
+        </is>
+      </c>
+      <c r="O19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr"/>
+      <c r="Q19" s="5" t="inlineStr"/>
+      <c r="R19" s="5" t="inlineStr"/>
+      <c r="S19" s="5" t="inlineStr"/>
+      <c r="T19" s="5" t="inlineStr"/>
+      <c r="U19" s="5" t="inlineStr"/>
       <c r="V19" s="5" t="inlineStr"/>
       <c r="W19" s="5" t="inlineStr"/>
       <c r="X19" s="5" t="inlineStr"/>
@@ -3648,25 +3699,26 @@
       </c>
       <c r="AG19" s="5" t="inlineStr"/>
       <c r="AH19" s="5" t="inlineStr"/>
-      <c r="AI19" s="3" t="inlineStr">
-        <is>
-          <t>复杂品类(60%+单个作图), 作图排3周</t>
+      <c r="AI19" s="3" t="inlineStr"/>
+      <c r="AJ19" s="3" t="inlineStr">
+        <is>
+          <t>小批次: 选款打分同周合并, 可直接定款</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>晚礼服 Evening</t>
+          <t>花童裙 Flower Girl</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>2026-11 批</t>
+          <t>2026-10 批</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="D20" s="5" t="inlineStr"/>
       <c r="E20" s="5" t="inlineStr"/>
@@ -3677,51 +3729,31 @@
       <c r="J20" s="5" t="inlineStr"/>
       <c r="K20" s="5" t="inlineStr"/>
       <c r="L20" s="5" t="inlineStr"/>
-      <c r="M20" s="12" t="inlineStr">
-        <is>
-          <t>选款</t>
-        </is>
-      </c>
-      <c r="N20" s="11" t="inlineStr">
-        <is>
-          <t>打分+定款</t>
+      <c r="M20" s="11" t="inlineStr">
+        <is>
+          <t>选款+打分+定款</t>
+        </is>
+      </c>
+      <c r="N20" s="10" t="inlineStr">
+        <is>
+          <t>SPU+作图</t>
         </is>
       </c>
       <c r="O20" s="10" t="inlineStr">
         <is>
-          <t>SPU+作图</t>
-        </is>
-      </c>
-      <c r="P20" s="10" t="inlineStr">
-        <is>
           <t>作图</t>
         </is>
       </c>
-      <c r="Q20" s="7" t="inlineStr">
-        <is>
-          <t>上架12</t>
-        </is>
-      </c>
-      <c r="R20" s="7" t="inlineStr">
-        <is>
-          <t>上架12</t>
-        </is>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>上架12</t>
-        </is>
-      </c>
-      <c r="T20" s="7" t="inlineStr">
-        <is>
-          <t>上架12</t>
-        </is>
-      </c>
-      <c r="U20" s="7" t="inlineStr">
-        <is>
-          <t>上架12</t>
-        </is>
-      </c>
+      <c r="P20" s="7" t="inlineStr">
+        <is>
+          <t>上架20</t>
+        </is>
+      </c>
+      <c r="Q20" s="5" t="inlineStr"/>
+      <c r="R20" s="5" t="inlineStr"/>
+      <c r="S20" s="5" t="inlineStr"/>
+      <c r="T20" s="5" t="inlineStr"/>
+      <c r="U20" s="5" t="inlineStr"/>
       <c r="V20" s="5" t="inlineStr"/>
       <c r="W20" s="5" t="inlineStr"/>
       <c r="X20" s="5" t="inlineStr"/>
@@ -3743,21 +3775,30 @@
       </c>
       <c r="AG20" s="5" t="inlineStr"/>
       <c r="AH20" s="5" t="inlineStr"/>
-      <c r="AI20" s="3" t="inlineStr"/>
+      <c r="AI20" s="12" t="inlineStr">
+        <is>
+          <t>定款周(10/5)与ED/BD 11月批选款撞期, 建议直接定款</t>
+        </is>
+      </c>
+      <c r="AJ20" s="3" t="inlineStr">
+        <is>
+          <t>小批次: 选款打分同周合并</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>婚纱 Bride</t>
+          <t>小伴娘裙 JBD</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>2026-11 批</t>
+          <t>2026-10 批</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D21" s="5" t="inlineStr"/>
       <c r="E21" s="5" t="inlineStr"/>
@@ -3766,57 +3807,33 @@
       <c r="H21" s="5" t="inlineStr"/>
       <c r="I21" s="5" t="inlineStr"/>
       <c r="J21" s="5" t="inlineStr"/>
-      <c r="K21" s="5" t="inlineStr"/>
-      <c r="L21" s="12" t="inlineStr">
-        <is>
-          <t>选款</t>
-        </is>
-      </c>
-      <c r="M21" s="11" t="inlineStr">
-        <is>
-          <t>打分+定款</t>
-        </is>
-      </c>
-      <c r="N21" s="10" t="inlineStr">
+      <c r="K21" s="10" t="inlineStr">
         <is>
           <t>SPU+作图</t>
         </is>
       </c>
-      <c r="O21" s="10" t="inlineStr">
+      <c r="L21" s="10" t="inlineStr">
         <is>
           <t>作图</t>
         </is>
       </c>
-      <c r="P21" s="10" t="inlineStr">
-        <is>
-          <t>作图</t>
-        </is>
-      </c>
-      <c r="Q21" s="7" t="inlineStr">
-        <is>
-          <t>上架8</t>
-        </is>
-      </c>
-      <c r="R21" s="7" t="inlineStr">
-        <is>
-          <t>上架8</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>上架8</t>
-        </is>
-      </c>
-      <c r="T21" s="7" t="inlineStr">
-        <is>
-          <t>上架8</t>
-        </is>
-      </c>
-      <c r="U21" s="7" t="inlineStr">
-        <is>
-          <t>上架8</t>
-        </is>
-      </c>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>上架15</t>
+        </is>
+      </c>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="7" t="inlineStr">
+        <is>
+          <t>上架15</t>
+        </is>
+      </c>
+      <c r="P21" s="5" t="inlineStr"/>
+      <c r="Q21" s="5" t="inlineStr"/>
+      <c r="R21" s="5" t="inlineStr"/>
+      <c r="S21" s="5" t="inlineStr"/>
+      <c r="T21" s="5" t="inlineStr"/>
+      <c r="U21" s="5" t="inlineStr"/>
       <c r="V21" s="5" t="inlineStr"/>
       <c r="W21" s="5" t="inlineStr"/>
       <c r="X21" s="5" t="inlineStr"/>
@@ -3838,16 +3855,17 @@
       </c>
       <c r="AG21" s="5" t="inlineStr"/>
       <c r="AH21" s="5" t="inlineStr"/>
-      <c r="AI21" s="3" t="inlineStr">
-        <is>
-          <t>复杂品类(60%+单个作图), 作图排3周</t>
+      <c r="AI21" s="3" t="inlineStr"/>
+      <c r="AJ21" s="3" t="inlineStr">
+        <is>
+          <t>已定款库存覆盖(50款库存之30款), 直接SPU+作图</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>伴娘裙 Bridesmaid</t>
+          <t>妈妈装 Mother of the Bride</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -3856,7 +3874,7 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D22" s="5" t="inlineStr"/>
       <c r="E22" s="5" t="inlineStr"/>
@@ -3866,20 +3884,24 @@
       <c r="I22" s="5" t="inlineStr"/>
       <c r="J22" s="5" t="inlineStr"/>
       <c r="K22" s="5" t="inlineStr"/>
-      <c r="L22" s="5" t="inlineStr"/>
-      <c r="M22" s="12" t="inlineStr">
+      <c r="L22" s="13" t="inlineStr">
         <is>
           <t>选款</t>
         </is>
       </c>
-      <c r="N22" s="11" t="inlineStr">
+      <c r="M22" s="11" t="inlineStr">
         <is>
           <t>打分+定款</t>
         </is>
       </c>
+      <c r="N22" s="10" t="inlineStr">
+        <is>
+          <t>SPU+作图</t>
+        </is>
+      </c>
       <c r="O22" s="10" t="inlineStr">
         <is>
-          <t>SPU+作图</t>
+          <t>作图</t>
         </is>
       </c>
       <c r="P22" s="10" t="inlineStr">
@@ -3889,27 +3911,27 @@
       </c>
       <c r="Q22" s="7" t="inlineStr">
         <is>
-          <t>上架10</t>
+          <t>上架20</t>
         </is>
       </c>
       <c r="R22" s="7" t="inlineStr">
         <is>
-          <t>上架10</t>
+          <t>上架20</t>
         </is>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>上架10</t>
+          <t>上架20</t>
         </is>
       </c>
       <c r="T22" s="7" t="inlineStr">
         <is>
-          <t>上架10</t>
+          <t>上架20</t>
         </is>
       </c>
       <c r="U22" s="7" t="inlineStr">
         <is>
-          <t>上架10</t>
+          <t>上架20</t>
         </is>
       </c>
       <c r="V22" s="5" t="inlineStr"/>
@@ -3934,11 +3956,16 @@
       <c r="AG22" s="5" t="inlineStr"/>
       <c r="AH22" s="5" t="inlineStr"/>
       <c r="AI22" s="3" t="inlineStr"/>
+      <c r="AJ22" s="3" t="inlineStr">
+        <is>
+          <t>复杂品类(60%+单个作图), 作图排3周</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>舞会裙 Prom</t>
+          <t>晚礼服 Evening</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -3947,7 +3974,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D23" s="5" t="inlineStr"/>
       <c r="E23" s="5" t="inlineStr"/>
@@ -3958,31 +3985,51 @@
       <c r="J23" s="5" t="inlineStr"/>
       <c r="K23" s="5" t="inlineStr"/>
       <c r="L23" s="5" t="inlineStr"/>
-      <c r="M23" s="5" t="inlineStr"/>
-      <c r="N23" s="5" t="inlineStr"/>
-      <c r="O23" s="11" t="inlineStr">
-        <is>
-          <t>选款+打分+定款</t>
+      <c r="M23" s="13" t="inlineStr">
+        <is>
+          <t>选款</t>
+        </is>
+      </c>
+      <c r="N23" s="11" t="inlineStr">
+        <is>
+          <t>打分+定款</t>
+        </is>
+      </c>
+      <c r="O23" s="10" t="inlineStr">
+        <is>
+          <t>SPU+作图</t>
         </is>
       </c>
       <c r="P23" s="10" t="inlineStr">
         <is>
-          <t>SPU+作图</t>
-        </is>
-      </c>
-      <c r="Q23" s="10" t="inlineStr">
-        <is>
           <t>作图</t>
         </is>
       </c>
+      <c r="Q23" s="7" t="inlineStr">
+        <is>
+          <t>上架12</t>
+        </is>
+      </c>
       <c r="R23" s="7" t="inlineStr">
         <is>
-          <t>上架20</t>
-        </is>
-      </c>
-      <c r="S23" s="5" t="inlineStr"/>
-      <c r="T23" s="5" t="inlineStr"/>
-      <c r="U23" s="5" t="inlineStr"/>
+          <t>上架12</t>
+        </is>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>上架12</t>
+        </is>
+      </c>
+      <c r="T23" s="7" t="inlineStr">
+        <is>
+          <t>上架12</t>
+        </is>
+      </c>
+      <c r="U23" s="7" t="inlineStr">
+        <is>
+          <t>上架12</t>
+        </is>
+      </c>
       <c r="V23" s="5" t="inlineStr"/>
       <c r="W23" s="5" t="inlineStr"/>
       <c r="X23" s="5" t="inlineStr"/>
@@ -4004,16 +4051,13 @@
       </c>
       <c r="AG23" s="5" t="inlineStr"/>
       <c r="AH23" s="5" t="inlineStr"/>
-      <c r="AI23" s="3" t="inlineStr">
-        <is>
-          <t>小批次: 选款打分同周合并, 可走直接定款再压缩1周</t>
-        </is>
-      </c>
+      <c r="AI23" s="3" t="inlineStr"/>
+      <c r="AJ23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>鸡尾酒裙 Cocktail</t>
+          <t>婚纱 Bride(选款)</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -4032,32 +4076,56 @@
       <c r="I24" s="5" t="inlineStr"/>
       <c r="J24" s="5" t="inlineStr"/>
       <c r="K24" s="5" t="inlineStr"/>
-      <c r="L24" s="5" t="inlineStr"/>
-      <c r="M24" s="5" t="inlineStr"/>
-      <c r="N24" s="5" t="inlineStr"/>
-      <c r="O24" s="5" t="inlineStr"/>
-      <c r="P24" s="11" t="inlineStr">
-        <is>
-          <t>选款+打分+定款</t>
-        </is>
-      </c>
-      <c r="Q24" s="10" t="inlineStr">
+      <c r="L24" s="13" t="inlineStr">
+        <is>
+          <t>选款</t>
+        </is>
+      </c>
+      <c r="M24" s="11" t="inlineStr">
+        <is>
+          <t>打分+定款</t>
+        </is>
+      </c>
+      <c r="N24" s="10" t="inlineStr">
         <is>
           <t>SPU+作图</t>
         </is>
       </c>
-      <c r="R24" s="10" t="inlineStr">
+      <c r="O24" s="10" t="inlineStr">
         <is>
           <t>作图</t>
         </is>
       </c>
+      <c r="P24" s="10" t="inlineStr">
+        <is>
+          <t>作图</t>
+        </is>
+      </c>
+      <c r="Q24" s="7" t="inlineStr">
+        <is>
+          <t>上架4</t>
+        </is>
+      </c>
+      <c r="R24" s="7" t="inlineStr">
+        <is>
+          <t>上架4</t>
+        </is>
+      </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>上架20</t>
-        </is>
-      </c>
-      <c r="T24" s="5" t="inlineStr"/>
-      <c r="U24" s="5" t="inlineStr"/>
+          <t>上架4</t>
+        </is>
+      </c>
+      <c r="T24" s="7" t="inlineStr">
+        <is>
+          <t>上架4</t>
+        </is>
+      </c>
+      <c r="U24" s="7" t="inlineStr">
+        <is>
+          <t>上架4</t>
+        </is>
+      </c>
       <c r="V24" s="5" t="inlineStr"/>
       <c r="W24" s="5" t="inlineStr"/>
       <c r="X24" s="5" t="inlineStr"/>
@@ -4079,16 +4147,17 @@
       </c>
       <c r="AG24" s="5" t="inlineStr"/>
       <c r="AH24" s="5" t="inlineStr"/>
-      <c r="AI24" s="3" t="inlineStr">
-        <is>
-          <t>小批次: 选款打分同周合并, 可走直接定款再压缩1周</t>
+      <c r="AI24" s="3" t="inlineStr"/>
+      <c r="AJ24" s="3" t="inlineStr">
+        <is>
+          <t>复杂品类, 作图排3周; 仅需定款计划量减去定制20款后的部分</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>花童裙 Flower Girl</t>
+          <t>婚纱 Bride(来图定制)</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -4097,7 +4166,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D25" s="5" t="inlineStr"/>
       <c r="E25" s="5" t="inlineStr"/>
@@ -4110,29 +4179,41 @@
       <c r="L25" s="5" t="inlineStr"/>
       <c r="M25" s="5" t="inlineStr"/>
       <c r="N25" s="5" t="inlineStr"/>
-      <c r="O25" s="5" t="inlineStr"/>
-      <c r="P25" s="5" t="inlineStr"/>
-      <c r="Q25" s="11" t="inlineStr">
-        <is>
-          <t>选款+打分+定款</t>
-        </is>
-      </c>
-      <c r="R25" s="10" t="inlineStr">
+      <c r="O25" s="10" t="inlineStr">
         <is>
           <t>SPU+作图</t>
         </is>
       </c>
-      <c r="S25" s="10" t="inlineStr">
+      <c r="P25" s="10" t="inlineStr">
         <is>
           <t>作图</t>
         </is>
       </c>
+      <c r="Q25" s="7" t="inlineStr">
+        <is>
+          <t>上架4</t>
+        </is>
+      </c>
+      <c r="R25" s="7" t="inlineStr">
+        <is>
+          <t>上架4</t>
+        </is>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>上架4</t>
+        </is>
+      </c>
       <c r="T25" s="7" t="inlineStr">
         <is>
-          <t>上架10</t>
-        </is>
-      </c>
-      <c r="U25" s="5" t="inlineStr"/>
+          <t>上架4</t>
+        </is>
+      </c>
+      <c r="U25" s="7" t="inlineStr">
+        <is>
+          <t>上架4</t>
+        </is>
+      </c>
       <c r="V25" s="5" t="inlineStr"/>
       <c r="W25" s="5" t="inlineStr"/>
       <c r="X25" s="5" t="inlineStr"/>
@@ -4154,25 +4235,26 @@
       </c>
       <c r="AG25" s="5" t="inlineStr"/>
       <c r="AH25" s="5" t="inlineStr"/>
-      <c r="AI25" s="3" t="inlineStr">
-        <is>
-          <t>小批次: 选款打分同周合并, 可走直接定款再压缩1周</t>
+      <c r="AI25" s="3" t="inlineStr"/>
+      <c r="AJ25" s="3" t="inlineStr">
+        <is>
+          <t>来图定制来源(月供约20款), 无需选款打分定款</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>妈妈装 Mother of the Bride</t>
+          <t>伴娘裙 Bridesmaid</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>2026-12 批</t>
+          <t>2026-11 批</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="D26" s="5" t="inlineStr"/>
       <c r="E26" s="5" t="inlineStr"/>
@@ -4183,55 +4265,55 @@
       <c r="J26" s="5" t="inlineStr"/>
       <c r="K26" s="5" t="inlineStr"/>
       <c r="L26" s="5" t="inlineStr"/>
-      <c r="M26" s="5" t="inlineStr"/>
-      <c r="N26" s="5" t="inlineStr"/>
-      <c r="O26" s="5" t="inlineStr"/>
-      <c r="P26" s="5" t="inlineStr"/>
-      <c r="Q26" s="12" t="inlineStr">
+      <c r="M26" s="13" t="inlineStr">
         <is>
           <t>选款</t>
         </is>
       </c>
-      <c r="R26" s="11" t="inlineStr">
+      <c r="N26" s="11" t="inlineStr">
         <is>
           <t>打分+定款</t>
         </is>
       </c>
-      <c r="S26" s="10" t="inlineStr">
+      <c r="O26" s="10" t="inlineStr">
         <is>
           <t>SPU+作图</t>
         </is>
       </c>
-      <c r="T26" s="10" t="inlineStr">
+      <c r="P26" s="10" t="inlineStr">
         <is>
           <t>作图</t>
         </is>
       </c>
-      <c r="U26" s="10" t="inlineStr">
-        <is>
-          <t>作图</t>
-        </is>
-      </c>
-      <c r="V26" s="7" t="inlineStr">
-        <is>
-          <t>上架20</t>
-        </is>
-      </c>
-      <c r="W26" s="7" t="inlineStr">
-        <is>
-          <t>上架20</t>
-        </is>
-      </c>
-      <c r="X26" s="7" t="inlineStr">
-        <is>
-          <t>上架20</t>
-        </is>
-      </c>
-      <c r="Y26" s="7" t="inlineStr">
-        <is>
-          <t>上架20</t>
-        </is>
-      </c>
+      <c r="Q26" s="7" t="inlineStr">
+        <is>
+          <t>上架10</t>
+        </is>
+      </c>
+      <c r="R26" s="7" t="inlineStr">
+        <is>
+          <t>上架10</t>
+        </is>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>上架10</t>
+        </is>
+      </c>
+      <c r="T26" s="7" t="inlineStr">
+        <is>
+          <t>上架10</t>
+        </is>
+      </c>
+      <c r="U26" s="7" t="inlineStr">
+        <is>
+          <t>上架10</t>
+        </is>
+      </c>
+      <c r="V26" s="5" t="inlineStr"/>
+      <c r="W26" s="5" t="inlineStr"/>
+      <c r="X26" s="5" t="inlineStr"/>
+      <c r="Y26" s="5" t="inlineStr"/>
       <c r="Z26" s="5" t="inlineStr"/>
       <c r="AA26" s="5" t="inlineStr"/>
       <c r="AB26" s="5" t="inlineStr"/>
@@ -4249,25 +4331,22 @@
       </c>
       <c r="AG26" s="5" t="inlineStr"/>
       <c r="AH26" s="5" t="inlineStr"/>
-      <c r="AI26" s="3" t="inlineStr">
-        <is>
-          <t>复杂品类(60%+单个作图), 作图排3周</t>
-        </is>
-      </c>
+      <c r="AI26" s="3" t="inlineStr"/>
+      <c r="AJ26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>晚礼服 Evening</t>
+          <t>舞会裙 Prom</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>2026-12 批</t>
+          <t>2026-11 批</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D27" s="5" t="inlineStr"/>
       <c r="E27" s="5" t="inlineStr"/>
@@ -4280,49 +4359,33 @@
       <c r="L27" s="5" t="inlineStr"/>
       <c r="M27" s="5" t="inlineStr"/>
       <c r="N27" s="5" t="inlineStr"/>
-      <c r="O27" s="5" t="inlineStr"/>
-      <c r="P27" s="5" t="inlineStr"/>
-      <c r="Q27" s="5" t="inlineStr"/>
-      <c r="R27" s="12" t="inlineStr">
-        <is>
-          <t>选款</t>
-        </is>
-      </c>
-      <c r="S27" s="11" t="inlineStr">
-        <is>
-          <t>打分+定款</t>
-        </is>
-      </c>
-      <c r="T27" s="10" t="inlineStr">
+      <c r="O27" s="11" t="inlineStr">
+        <is>
+          <t>选款+打分+定款</t>
+        </is>
+      </c>
+      <c r="P27" s="10" t="inlineStr">
         <is>
           <t>SPU+作图</t>
         </is>
       </c>
-      <c r="U27" s="10" t="inlineStr">
+      <c r="Q27" s="10" t="inlineStr">
         <is>
           <t>作图</t>
         </is>
       </c>
-      <c r="V27" s="7" t="inlineStr">
-        <is>
-          <t>上架13</t>
-        </is>
-      </c>
-      <c r="W27" s="7" t="inlineStr">
-        <is>
-          <t>上架13</t>
-        </is>
-      </c>
-      <c r="X27" s="7" t="inlineStr">
-        <is>
-          <t>上架12</t>
-        </is>
-      </c>
-      <c r="Y27" s="7" t="inlineStr">
-        <is>
-          <t>上架12</t>
-        </is>
-      </c>
+      <c r="R27" s="7" t="inlineStr">
+        <is>
+          <t>上架20</t>
+        </is>
+      </c>
+      <c r="S27" s="5" t="inlineStr"/>
+      <c r="T27" s="5" t="inlineStr"/>
+      <c r="U27" s="5" t="inlineStr"/>
+      <c r="V27" s="5" t="inlineStr"/>
+      <c r="W27" s="5" t="inlineStr"/>
+      <c r="X27" s="5" t="inlineStr"/>
+      <c r="Y27" s="5" t="inlineStr"/>
       <c r="Z27" s="5" t="inlineStr"/>
       <c r="AA27" s="5" t="inlineStr"/>
       <c r="AB27" s="5" t="inlineStr"/>
@@ -4341,20 +4404,25 @@
       <c r="AG27" s="5" t="inlineStr"/>
       <c r="AH27" s="5" t="inlineStr"/>
       <c r="AI27" s="3" t="inlineStr"/>
+      <c r="AJ27" s="3" t="inlineStr">
+        <is>
+          <t>新品类首批, 小批次: 选款打分同周合并</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>婚纱 Bride</t>
+          <t>鸡尾酒裙 Cocktail</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>2026-12 批</t>
+          <t>2026-11 批</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D28" s="5" t="inlineStr"/>
       <c r="E28" s="5" t="inlineStr"/>
@@ -4368,30 +4436,30 @@
       <c r="M28" s="5" t="inlineStr"/>
       <c r="N28" s="5" t="inlineStr"/>
       <c r="O28" s="5" t="inlineStr"/>
-      <c r="P28" s="5" t="inlineStr"/>
-      <c r="Q28" s="5" t="inlineStr"/>
-      <c r="R28" s="5" t="inlineStr"/>
-      <c r="S28" s="5" t="inlineStr"/>
-      <c r="T28" s="11" t="inlineStr">
+      <c r="P28" s="11" t="inlineStr">
         <is>
           <t>选款+打分+定款</t>
         </is>
       </c>
-      <c r="U28" s="10" t="inlineStr">
+      <c r="Q28" s="10" t="inlineStr">
         <is>
           <t>SPU+作图</t>
         </is>
       </c>
-      <c r="V28" s="10" t="inlineStr">
+      <c r="R28" s="10" t="inlineStr">
         <is>
           <t>作图</t>
         </is>
       </c>
-      <c r="W28" s="7" t="inlineStr">
-        <is>
-          <t>上架10</t>
-        </is>
-      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>上架20</t>
+        </is>
+      </c>
+      <c r="T28" s="5" t="inlineStr"/>
+      <c r="U28" s="5" t="inlineStr"/>
+      <c r="V28" s="5" t="inlineStr"/>
+      <c r="W28" s="5" t="inlineStr"/>
       <c r="X28" s="5" t="inlineStr"/>
       <c r="Y28" s="5" t="inlineStr"/>
       <c r="Z28" s="5" t="inlineStr"/>
@@ -4411,25 +4479,26 @@
       </c>
       <c r="AG28" s="5" t="inlineStr"/>
       <c r="AH28" s="5" t="inlineStr"/>
-      <c r="AI28" s="3" t="inlineStr">
-        <is>
-          <t>小批次: 选款打分同周合并, 可走直接定款再压缩1周</t>
+      <c r="AI28" s="3" t="inlineStr"/>
+      <c r="AJ28" s="3" t="inlineStr">
+        <is>
+          <t>小批次: 选款打分同周合并, 可直接定款</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>伴娘裙 Bridesmaid</t>
+          <t>花童裙 Flower Girl</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>2026-12 批</t>
+          <t>2026-11 批</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="D29" s="5" t="inlineStr"/>
       <c r="E29" s="5" t="inlineStr"/>
@@ -4444,47 +4513,31 @@
       <c r="N29" s="5" t="inlineStr"/>
       <c r="O29" s="5" t="inlineStr"/>
       <c r="P29" s="5" t="inlineStr"/>
-      <c r="Q29" s="5" t="inlineStr"/>
-      <c r="R29" s="12" t="inlineStr">
-        <is>
-          <t>选款</t>
-        </is>
-      </c>
-      <c r="S29" s="11" t="inlineStr">
-        <is>
-          <t>打分+定款</t>
-        </is>
-      </c>
-      <c r="T29" s="10" t="inlineStr">
+      <c r="Q29" s="11" t="inlineStr">
+        <is>
+          <t>选款+打分+定款</t>
+        </is>
+      </c>
+      <c r="R29" s="10" t="inlineStr">
         <is>
           <t>SPU+作图</t>
         </is>
       </c>
-      <c r="U29" s="10" t="inlineStr">
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>作图</t>
         </is>
       </c>
-      <c r="V29" s="7" t="inlineStr">
+      <c r="T29" s="7" t="inlineStr">
         <is>
           <t>上架10</t>
         </is>
       </c>
-      <c r="W29" s="7" t="inlineStr">
-        <is>
-          <t>上架10</t>
-        </is>
-      </c>
-      <c r="X29" s="7" t="inlineStr">
-        <is>
-          <t>上架10</t>
-        </is>
-      </c>
-      <c r="Y29" s="7" t="inlineStr">
-        <is>
-          <t>上架10</t>
-        </is>
-      </c>
+      <c r="U29" s="5" t="inlineStr"/>
+      <c r="V29" s="5" t="inlineStr"/>
+      <c r="W29" s="5" t="inlineStr"/>
+      <c r="X29" s="5" t="inlineStr"/>
+      <c r="Y29" s="5" t="inlineStr"/>
       <c r="Z29" s="5" t="inlineStr"/>
       <c r="AA29" s="5" t="inlineStr"/>
       <c r="AB29" s="5" t="inlineStr"/>
@@ -4502,12 +4555,21 @@
       </c>
       <c r="AG29" s="5" t="inlineStr"/>
       <c r="AH29" s="5" t="inlineStr"/>
-      <c r="AI29" s="3" t="inlineStr"/>
+      <c r="AI29" s="12" t="inlineStr">
+        <is>
+          <t>定款周(11/2)与MBD/Prom 12月批选款撞期, 建议直接定款</t>
+        </is>
+      </c>
+      <c r="AJ29" s="3" t="inlineStr">
+        <is>
+          <t>小批次: 选款打分同周合并</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>舞会裙 Prom</t>
+          <t>妈妈装 Mother of the Bride</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -4516,7 +4578,7 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="D30" s="5" t="inlineStr"/>
       <c r="E30" s="5" t="inlineStr"/>
@@ -4531,20 +4593,24 @@
       <c r="N30" s="5" t="inlineStr"/>
       <c r="O30" s="5" t="inlineStr"/>
       <c r="P30" s="5" t="inlineStr"/>
-      <c r="Q30" s="5" t="inlineStr"/>
-      <c r="R30" s="12" t="inlineStr">
+      <c r="Q30" s="13" t="inlineStr">
         <is>
           <t>选款</t>
         </is>
       </c>
-      <c r="S30" s="11" t="inlineStr">
+      <c r="R30" s="11" t="inlineStr">
         <is>
           <t>打分+定款</t>
         </is>
       </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>SPU+作图</t>
+        </is>
+      </c>
       <c r="T30" s="10" t="inlineStr">
         <is>
-          <t>SPU+作图</t>
+          <t>作图</t>
         </is>
       </c>
       <c r="U30" s="10" t="inlineStr">
@@ -4554,22 +4620,22 @@
       </c>
       <c r="V30" s="7" t="inlineStr">
         <is>
-          <t>上架10</t>
+          <t>上架20</t>
         </is>
       </c>
       <c r="W30" s="7" t="inlineStr">
         <is>
-          <t>上架10</t>
+          <t>上架20</t>
         </is>
       </c>
       <c r="X30" s="7" t="inlineStr">
         <is>
-          <t>上架10</t>
+          <t>上架20</t>
         </is>
       </c>
       <c r="Y30" s="7" t="inlineStr">
         <is>
-          <t>上架10</t>
+          <t>上架20</t>
         </is>
       </c>
       <c r="Z30" s="5" t="inlineStr"/>
@@ -4590,11 +4656,16 @@
       <c r="AG30" s="5" t="inlineStr"/>
       <c r="AH30" s="5" t="inlineStr"/>
       <c r="AI30" s="3" t="inlineStr"/>
+      <c r="AJ30" s="3" t="inlineStr">
+        <is>
+          <t>复杂品类(60%+单个作图), 作图排3周</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>鸡尾酒裙 Cocktail</t>
+          <t>晚礼服 Evening</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -4603,7 +4674,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D31" s="5" t="inlineStr"/>
       <c r="E31" s="5" t="inlineStr"/>
@@ -4619,10 +4690,14 @@
       <c r="O31" s="5" t="inlineStr"/>
       <c r="P31" s="5" t="inlineStr"/>
       <c r="Q31" s="5" t="inlineStr"/>
-      <c r="R31" s="5" t="inlineStr"/>
+      <c r="R31" s="13" t="inlineStr">
+        <is>
+          <t>选款</t>
+        </is>
+      </c>
       <c r="S31" s="11" t="inlineStr">
         <is>
-          <t>选款+打分+定款</t>
+          <t>打分+定款</t>
         </is>
       </c>
       <c r="T31" s="10" t="inlineStr">
@@ -4637,12 +4712,24 @@
       </c>
       <c r="V31" s="7" t="inlineStr">
         <is>
-          <t>上架20</t>
-        </is>
-      </c>
-      <c r="W31" s="5" t="inlineStr"/>
-      <c r="X31" s="5" t="inlineStr"/>
-      <c r="Y31" s="5" t="inlineStr"/>
+          <t>上架13</t>
+        </is>
+      </c>
+      <c r="W31" s="7" t="inlineStr">
+        <is>
+          <t>上架13</t>
+        </is>
+      </c>
+      <c r="X31" s="7" t="inlineStr">
+        <is>
+          <t>上架12</t>
+        </is>
+      </c>
+      <c r="Y31" s="7" t="inlineStr">
+        <is>
+          <t>上架12</t>
+        </is>
+      </c>
       <c r="Z31" s="5" t="inlineStr"/>
       <c r="AA31" s="5" t="inlineStr"/>
       <c r="AB31" s="5" t="inlineStr"/>
@@ -4660,16 +4747,13 @@
       </c>
       <c r="AG31" s="5" t="inlineStr"/>
       <c r="AH31" s="5" t="inlineStr"/>
-      <c r="AI31" s="3" t="inlineStr">
-        <is>
-          <t>小批次: 选款打分同周合并, 可走直接定款再压缩1周</t>
-        </is>
-      </c>
+      <c r="AI31" s="3" t="inlineStr"/>
+      <c r="AJ31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>花童裙 Flower Girl</t>
+          <t>婚纱 Bride(来图定制)</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -4678,7 +4762,7 @@
         </is>
       </c>
       <c r="C32" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D32" s="5" t="inlineStr"/>
       <c r="E32" s="5" t="inlineStr"/>
@@ -4697,26 +4781,22 @@
       <c r="R32" s="5" t="inlineStr"/>
       <c r="S32" s="5" t="inlineStr"/>
       <c r="T32" s="5" t="inlineStr"/>
-      <c r="U32" s="11" t="inlineStr">
-        <is>
-          <t>选款+打分+定款</t>
+      <c r="U32" s="10" t="inlineStr">
+        <is>
+          <t>SPU+作图</t>
         </is>
       </c>
       <c r="V32" s="10" t="inlineStr">
         <is>
-          <t>SPU+作图</t>
-        </is>
-      </c>
-      <c r="W32" s="10" t="inlineStr">
-        <is>
           <t>作图</t>
         </is>
       </c>
-      <c r="X32" s="7" t="inlineStr">
-        <is>
-          <t>上架20</t>
-        </is>
-      </c>
+      <c r="W32" s="7" t="inlineStr">
+        <is>
+          <t>上架10</t>
+        </is>
+      </c>
+      <c r="X32" s="5" t="inlineStr"/>
       <c r="Y32" s="5" t="inlineStr"/>
       <c r="Z32" s="5" t="inlineStr"/>
       <c r="AA32" s="5" t="inlineStr"/>
@@ -4735,16 +4815,17 @@
       </c>
       <c r="AG32" s="5" t="inlineStr"/>
       <c r="AH32" s="5" t="inlineStr"/>
-      <c r="AI32" s="3" t="inlineStr">
-        <is>
-          <t>小批次: 选款打分同周合并, 可走直接定款再压缩1周</t>
+      <c r="AI32" s="3" t="inlineStr"/>
+      <c r="AJ32" s="3" t="inlineStr">
+        <is>
+          <t>来图定制来源(月供约20款), 无需选款打分定款</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>小伴娘裙 JBD</t>
+          <t>伴娘裙 Bridesmaid</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -4753,7 +4834,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D33" s="5" t="inlineStr"/>
       <c r="E33" s="5" t="inlineStr"/>
@@ -4769,28 +4850,44 @@
       <c r="O33" s="5" t="inlineStr"/>
       <c r="P33" s="5" t="inlineStr"/>
       <c r="Q33" s="5" t="inlineStr"/>
-      <c r="R33" s="5" t="inlineStr"/>
-      <c r="S33" s="5" t="inlineStr"/>
-      <c r="T33" s="5" t="inlineStr"/>
-      <c r="U33" s="5" t="inlineStr"/>
-      <c r="V33" s="11" t="inlineStr">
-        <is>
-          <t>选款+打分+定款</t>
-        </is>
-      </c>
-      <c r="W33" s="10" t="inlineStr">
+      <c r="R33" s="13" t="inlineStr">
+        <is>
+          <t>选款</t>
+        </is>
+      </c>
+      <c r="S33" s="11" t="inlineStr">
+        <is>
+          <t>打分+定款</t>
+        </is>
+      </c>
+      <c r="T33" s="10" t="inlineStr">
         <is>
           <t>SPU+作图</t>
         </is>
       </c>
-      <c r="X33" s="10" t="inlineStr">
+      <c r="U33" s="10" t="inlineStr">
         <is>
           <t>作图</t>
         </is>
       </c>
+      <c r="V33" s="7" t="inlineStr">
+        <is>
+          <t>上架10</t>
+        </is>
+      </c>
+      <c r="W33" s="7" t="inlineStr">
+        <is>
+          <t>上架10</t>
+        </is>
+      </c>
+      <c r="X33" s="7" t="inlineStr">
+        <is>
+          <t>上架10</t>
+        </is>
+      </c>
       <c r="Y33" s="7" t="inlineStr">
         <is>
-          <t>上架20</t>
+          <t>上架10</t>
         </is>
       </c>
       <c r="Z33" s="5" t="inlineStr"/>
@@ -4810,25 +4907,22 @@
       </c>
       <c r="AG33" s="5" t="inlineStr"/>
       <c r="AH33" s="5" t="inlineStr"/>
-      <c r="AI33" s="3" t="inlineStr">
-        <is>
-          <t>小批次: 选款打分同周合并, 可走直接定款再压缩1周</t>
-        </is>
-      </c>
+      <c r="AI33" s="3" t="inlineStr"/>
+      <c r="AJ33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>妈妈装 Mother of the Bride</t>
+          <t>舞会裙 Prom</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>2027-01 批</t>
+          <t>2026-12 批</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="D34" s="5" t="inlineStr"/>
       <c r="E34" s="5" t="inlineStr"/>
@@ -4843,55 +4937,55 @@
       <c r="N34" s="5" t="inlineStr"/>
       <c r="O34" s="5" t="inlineStr"/>
       <c r="P34" s="5" t="inlineStr"/>
-      <c r="Q34" s="5" t="inlineStr"/>
-      <c r="R34" s="5" t="inlineStr"/>
-      <c r="S34" s="5" t="inlineStr"/>
-      <c r="T34" s="5" t="inlineStr"/>
-      <c r="U34" s="12" t="inlineStr">
+      <c r="Q34" s="13" t="inlineStr">
         <is>
           <t>选款</t>
         </is>
       </c>
-      <c r="V34" s="11" t="inlineStr">
+      <c r="R34" s="11" t="inlineStr">
         <is>
           <t>打分+定款</t>
         </is>
       </c>
-      <c r="W34" s="10" t="inlineStr">
-        <is>
-          <t>SPU+作图</t>
-        </is>
-      </c>
-      <c r="X34" s="10" t="inlineStr">
+      <c r="S34" s="14" t="inlineStr">
+        <is>
+          <t>SPU</t>
+        </is>
+      </c>
+      <c r="T34" s="10" t="inlineStr">
         <is>
           <t>作图</t>
         </is>
       </c>
-      <c r="Y34" s="10" t="inlineStr">
+      <c r="U34" s="10" t="inlineStr">
         <is>
           <t>作图</t>
         </is>
       </c>
-      <c r="Z34" s="7" t="inlineStr">
-        <is>
-          <t>上架20</t>
-        </is>
-      </c>
-      <c r="AA34" s="7" t="inlineStr">
-        <is>
-          <t>上架20</t>
-        </is>
-      </c>
-      <c r="AB34" s="7" t="inlineStr">
-        <is>
-          <t>上架20</t>
-        </is>
-      </c>
-      <c r="AC34" s="7" t="inlineStr">
-        <is>
-          <t>上架20</t>
-        </is>
-      </c>
+      <c r="V34" s="7" t="inlineStr">
+        <is>
+          <t>上架10</t>
+        </is>
+      </c>
+      <c r="W34" s="7" t="inlineStr">
+        <is>
+          <t>上架10</t>
+        </is>
+      </c>
+      <c r="X34" s="7" t="inlineStr">
+        <is>
+          <t>上架10</t>
+        </is>
+      </c>
+      <c r="Y34" s="7" t="inlineStr">
+        <is>
+          <t>上架10</t>
+        </is>
+      </c>
+      <c r="Z34" s="5" t="inlineStr"/>
+      <c r="AA34" s="5" t="inlineStr"/>
+      <c r="AB34" s="5" t="inlineStr"/>
+      <c r="AC34" s="5" t="inlineStr"/>
       <c r="AD34" s="5" t="inlineStr"/>
       <c r="AE34" s="8" t="inlineStr">
         <is>
@@ -4905,25 +4999,26 @@
       </c>
       <c r="AG34" s="5" t="inlineStr"/>
       <c r="AH34" s="5" t="inlineStr"/>
-      <c r="AI34" s="3" t="inlineStr">
-        <is>
-          <t>复杂品类(60%+单个作图), 作图排3周</t>
+      <c r="AI34" s="3" t="inlineStr"/>
+      <c r="AJ34" s="3" t="inlineStr">
+        <is>
+          <t>选款提前至前5周, 与ED/BD错峰</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>晚礼服 Evening</t>
+          <t>鸡尾酒裙 Cocktail</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>2027-01 批</t>
+          <t>2026-12 批</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D35" s="5" t="inlineStr"/>
       <c r="E35" s="5" t="inlineStr"/>
@@ -4940,49 +5035,33 @@
       <c r="P35" s="5" t="inlineStr"/>
       <c r="Q35" s="5" t="inlineStr"/>
       <c r="R35" s="5" t="inlineStr"/>
-      <c r="S35" s="5" t="inlineStr"/>
-      <c r="T35" s="5" t="inlineStr"/>
-      <c r="U35" s="5" t="inlineStr"/>
-      <c r="V35" s="12" t="inlineStr">
-        <is>
-          <t>选款</t>
-        </is>
-      </c>
-      <c r="W35" s="11" t="inlineStr">
-        <is>
-          <t>打分+定款</t>
-        </is>
-      </c>
-      <c r="X35" s="10" t="inlineStr">
+      <c r="S35" s="11" t="inlineStr">
+        <is>
+          <t>选款+打分+定款</t>
+        </is>
+      </c>
+      <c r="T35" s="10" t="inlineStr">
         <is>
           <t>SPU+作图</t>
         </is>
       </c>
-      <c r="Y35" s="10" t="inlineStr">
+      <c r="U35" s="10" t="inlineStr">
         <is>
           <t>作图</t>
         </is>
       </c>
-      <c r="Z35" s="7" t="inlineStr">
-        <is>
-          <t>上架10</t>
-        </is>
-      </c>
-      <c r="AA35" s="7" t="inlineStr">
-        <is>
-          <t>上架10</t>
-        </is>
-      </c>
-      <c r="AB35" s="7" t="inlineStr">
-        <is>
-          <t>上架10</t>
-        </is>
-      </c>
-      <c r="AC35" s="7" t="inlineStr">
-        <is>
-          <t>上架10</t>
-        </is>
-      </c>
+      <c r="V35" s="7" t="inlineStr">
+        <is>
+          <t>上架20</t>
+        </is>
+      </c>
+      <c r="W35" s="5" t="inlineStr"/>
+      <c r="X35" s="5" t="inlineStr"/>
+      <c r="Y35" s="5" t="inlineStr"/>
+      <c r="Z35" s="5" t="inlineStr"/>
+      <c r="AA35" s="5" t="inlineStr"/>
+      <c r="AB35" s="5" t="inlineStr"/>
+      <c r="AC35" s="5" t="inlineStr"/>
       <c r="AD35" s="5" t="inlineStr"/>
       <c r="AE35" s="8" t="inlineStr">
         <is>
@@ -4997,20 +5076,25 @@
       <c r="AG35" s="5" t="inlineStr"/>
       <c r="AH35" s="5" t="inlineStr"/>
       <c r="AI35" s="3" t="inlineStr"/>
+      <c r="AJ35" s="3" t="inlineStr">
+        <is>
+          <t>小批次: 选款打分同周合并, 可直接定款</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>婚纱 Bride</t>
+          <t>花童裙 Flower Girl</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>2027-01 批</t>
+          <t>2026-12 批</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D36" s="5" t="inlineStr"/>
       <c r="E36" s="5" t="inlineStr"/>
@@ -5029,29 +5113,29 @@
       <c r="R36" s="5" t="inlineStr"/>
       <c r="S36" s="5" t="inlineStr"/>
       <c r="T36" s="5" t="inlineStr"/>
-      <c r="U36" s="5" t="inlineStr"/>
-      <c r="V36" s="5" t="inlineStr"/>
-      <c r="W36" s="5" t="inlineStr"/>
-      <c r="X36" s="11" t="inlineStr">
+      <c r="U36" s="11" t="inlineStr">
         <is>
           <t>选款+打分+定款</t>
         </is>
       </c>
-      <c r="Y36" s="10" t="inlineStr">
+      <c r="V36" s="10" t="inlineStr">
         <is>
           <t>SPU+作图</t>
         </is>
       </c>
-      <c r="Z36" s="10" t="inlineStr">
+      <c r="W36" s="10" t="inlineStr">
         <is>
           <t>作图</t>
         </is>
       </c>
-      <c r="AA36" s="7" t="inlineStr">
-        <is>
-          <t>上架10</t>
-        </is>
-      </c>
+      <c r="X36" s="7" t="inlineStr">
+        <is>
+          <t>上架20</t>
+        </is>
+      </c>
+      <c r="Y36" s="5" t="inlineStr"/>
+      <c r="Z36" s="5" t="inlineStr"/>
+      <c r="AA36" s="5" t="inlineStr"/>
       <c r="AB36" s="5" t="inlineStr"/>
       <c r="AC36" s="5" t="inlineStr"/>
       <c r="AD36" s="5" t="inlineStr"/>
@@ -5067,25 +5151,30 @@
       </c>
       <c r="AG36" s="5" t="inlineStr"/>
       <c r="AH36" s="5" t="inlineStr"/>
-      <c r="AI36" s="3" t="inlineStr">
-        <is>
-          <t>小批次: 选款打分同周合并, 可走直接定款再压缩1周</t>
+      <c r="AI36" s="12" t="inlineStr">
+        <is>
+          <t>定款周(11/30)与MBD/Prom 1月批选款撞期, 建议直接定款</t>
+        </is>
+      </c>
+      <c r="AJ36" s="3" t="inlineStr">
+        <is>
+          <t>小批次: 选款打分同周合并</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>伴娘裙 Bridesmaid</t>
+          <t>小伴娘裙 JBD</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>2027-01 批</t>
+          <t>2026-12 批</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D37" s="5" t="inlineStr"/>
       <c r="E37" s="5" t="inlineStr"/>
@@ -5105,46 +5194,30 @@
       <c r="S37" s="5" t="inlineStr"/>
       <c r="T37" s="5" t="inlineStr"/>
       <c r="U37" s="5" t="inlineStr"/>
-      <c r="V37" s="12" t="inlineStr">
-        <is>
-          <t>选款</t>
-        </is>
-      </c>
-      <c r="W37" s="11" t="inlineStr">
-        <is>
-          <t>打分+定款</t>
+      <c r="V37" s="11" t="inlineStr">
+        <is>
+          <t>选款+打分+定款</t>
+        </is>
+      </c>
+      <c r="W37" s="10" t="inlineStr">
+        <is>
+          <t>SPU+作图</t>
         </is>
       </c>
       <c r="X37" s="10" t="inlineStr">
         <is>
-          <t>SPU+作图</t>
-        </is>
-      </c>
-      <c r="Y37" s="10" t="inlineStr">
-        <is>
           <t>作图</t>
         </is>
       </c>
-      <c r="Z37" s="7" t="inlineStr">
-        <is>
-          <t>上架10</t>
-        </is>
-      </c>
-      <c r="AA37" s="7" t="inlineStr">
-        <is>
-          <t>上架10</t>
-        </is>
-      </c>
-      <c r="AB37" s="7" t="inlineStr">
-        <is>
-          <t>上架10</t>
-        </is>
-      </c>
-      <c r="AC37" s="7" t="inlineStr">
-        <is>
-          <t>上架10</t>
-        </is>
-      </c>
+      <c r="Y37" s="7" t="inlineStr">
+        <is>
+          <t>上架20</t>
+        </is>
+      </c>
+      <c r="Z37" s="5" t="inlineStr"/>
+      <c r="AA37" s="5" t="inlineStr"/>
+      <c r="AB37" s="5" t="inlineStr"/>
+      <c r="AC37" s="5" t="inlineStr"/>
       <c r="AD37" s="5" t="inlineStr"/>
       <c r="AE37" s="8" t="inlineStr">
         <is>
@@ -5158,12 +5231,21 @@
       </c>
       <c r="AG37" s="5" t="inlineStr"/>
       <c r="AH37" s="5" t="inlineStr"/>
-      <c r="AI37" s="3" t="inlineStr"/>
+      <c r="AI37" s="12" t="inlineStr">
+        <is>
+          <t>定款周(12/7)与ED/BD 1月批选款撞期, 建议直接定款</t>
+        </is>
+      </c>
+      <c r="AJ37" s="3" t="inlineStr">
+        <is>
+          <t>小批次: 选款打分同周合并</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>舞会裙 Prom</t>
+          <t>妈妈装 Mother of the Bride</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
@@ -5172,7 +5254,7 @@
         </is>
       </c>
       <c r="C38" s="5" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="D38" s="5" t="inlineStr"/>
       <c r="E38" s="5" t="inlineStr"/>
@@ -5191,20 +5273,24 @@
       <c r="R38" s="5" t="inlineStr"/>
       <c r="S38" s="5" t="inlineStr"/>
       <c r="T38" s="5" t="inlineStr"/>
-      <c r="U38" s="5" t="inlineStr"/>
-      <c r="V38" s="12" t="inlineStr">
+      <c r="U38" s="13" t="inlineStr">
         <is>
           <t>选款</t>
         </is>
       </c>
-      <c r="W38" s="11" t="inlineStr">
+      <c r="V38" s="11" t="inlineStr">
         <is>
           <t>打分+定款</t>
         </is>
       </c>
+      <c r="W38" s="10" t="inlineStr">
+        <is>
+          <t>SPU+作图</t>
+        </is>
+      </c>
       <c r="X38" s="10" t="inlineStr">
         <is>
-          <t>SPU+作图</t>
+          <t>作图</t>
         </is>
       </c>
       <c r="Y38" s="10" t="inlineStr">
@@ -5214,22 +5300,22 @@
       </c>
       <c r="Z38" s="7" t="inlineStr">
         <is>
-          <t>上架10</t>
+          <t>上架20</t>
         </is>
       </c>
       <c r="AA38" s="7" t="inlineStr">
         <is>
-          <t>上架10</t>
+          <t>上架20</t>
         </is>
       </c>
       <c r="AB38" s="7" t="inlineStr">
         <is>
-          <t>上架10</t>
+          <t>上架20</t>
         </is>
       </c>
       <c r="AC38" s="7" t="inlineStr">
         <is>
-          <t>上架10</t>
+          <t>上架20</t>
         </is>
       </c>
       <c r="AD38" s="5" t="inlineStr"/>
@@ -5246,11 +5332,16 @@
       <c r="AG38" s="5" t="inlineStr"/>
       <c r="AH38" s="5" t="inlineStr"/>
       <c r="AI38" s="3" t="inlineStr"/>
+      <c r="AJ38" s="3" t="inlineStr">
+        <is>
+          <t>复杂品类(60%+单个作图), 作图排3周</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>鸡尾酒裙 Cocktail</t>
+          <t>晚礼服 Evening</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
@@ -5259,7 +5350,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D39" s="5" t="inlineStr"/>
       <c r="E39" s="5" t="inlineStr"/>
@@ -5279,7 +5370,7 @@
       <c r="S39" s="5" t="inlineStr"/>
       <c r="T39" s="5" t="inlineStr"/>
       <c r="U39" s="5" t="inlineStr"/>
-      <c r="V39" s="12" t="inlineStr">
+      <c r="V39" s="13" t="inlineStr">
         <is>
           <t>选款</t>
         </is>
@@ -5301,16 +5392,24 @@
       </c>
       <c r="Z39" s="7" t="inlineStr">
         <is>
-          <t>上架15</t>
-        </is>
-      </c>
-      <c r="AA39" s="5" t="inlineStr"/>
+          <t>上架10</t>
+        </is>
+      </c>
+      <c r="AA39" s="7" t="inlineStr">
+        <is>
+          <t>上架10</t>
+        </is>
+      </c>
       <c r="AB39" s="7" t="inlineStr">
         <is>
-          <t>上架15</t>
-        </is>
-      </c>
-      <c r="AC39" s="5" t="inlineStr"/>
+          <t>上架10</t>
+        </is>
+      </c>
+      <c r="AC39" s="7" t="inlineStr">
+        <is>
+          <t>上架10</t>
+        </is>
+      </c>
       <c r="AD39" s="5" t="inlineStr"/>
       <c r="AE39" s="8" t="inlineStr">
         <is>
@@ -5325,11 +5424,12 @@
       <c r="AG39" s="5" t="inlineStr"/>
       <c r="AH39" s="5" t="inlineStr"/>
       <c r="AI39" s="3" t="inlineStr"/>
+      <c r="AJ39" s="3" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>花童裙 Flower Girl</t>
+          <t>婚纱 Bride(来图定制)</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
@@ -5338,7 +5438,7 @@
         </is>
       </c>
       <c r="C40" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D40" s="5" t="inlineStr"/>
       <c r="E40" s="5" t="inlineStr"/>
@@ -5360,28 +5460,24 @@
       <c r="U40" s="5" t="inlineStr"/>
       <c r="V40" s="5" t="inlineStr"/>
       <c r="W40" s="5" t="inlineStr"/>
-      <c r="X40" s="5" t="inlineStr"/>
-      <c r="Y40" s="5" t="inlineStr"/>
-      <c r="Z40" s="11" t="inlineStr">
-        <is>
-          <t>选款+打分+定款</t>
-        </is>
-      </c>
-      <c r="AA40" s="10" t="inlineStr">
+      <c r="X40" s="10" t="inlineStr">
         <is>
           <t>SPU+作图</t>
         </is>
       </c>
-      <c r="AB40" s="10" t="inlineStr">
+      <c r="Y40" s="10" t="inlineStr">
         <is>
           <t>作图</t>
         </is>
       </c>
-      <c r="AC40" s="7" t="inlineStr">
-        <is>
-          <t>上架20</t>
-        </is>
-      </c>
+      <c r="Z40" s="7" t="inlineStr">
+        <is>
+          <t>上架10</t>
+        </is>
+      </c>
+      <c r="AA40" s="5" t="inlineStr"/>
+      <c r="AB40" s="5" t="inlineStr"/>
+      <c r="AC40" s="5" t="inlineStr"/>
       <c r="AD40" s="5" t="inlineStr"/>
       <c r="AE40" s="8" t="inlineStr">
         <is>
@@ -5395,25 +5491,26 @@
       </c>
       <c r="AG40" s="5" t="inlineStr"/>
       <c r="AH40" s="5" t="inlineStr"/>
-      <c r="AI40" s="3" t="inlineStr">
-        <is>
-          <t>小批次: 选款打分同周合并, 可走直接定款再压缩1周</t>
+      <c r="AI40" s="3" t="inlineStr"/>
+      <c r="AJ40" s="3" t="inlineStr">
+        <is>
+          <t>来图定制来源(月供约20款), 无需选款打分定款</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>妈妈装 Mother of the Bride</t>
+          <t>伴娘裙 Bridesmaid</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>2027-02 批</t>
+          <t>2027-01 批</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D41" s="5" t="inlineStr"/>
       <c r="E41" s="5" t="inlineStr"/>
@@ -5433,39 +5530,47 @@
       <c r="S41" s="5" t="inlineStr"/>
       <c r="T41" s="5" t="inlineStr"/>
       <c r="U41" s="5" t="inlineStr"/>
-      <c r="V41" s="5" t="inlineStr"/>
-      <c r="W41" s="5" t="inlineStr"/>
-      <c r="X41" s="5" t="inlineStr"/>
-      <c r="Y41" s="12" t="inlineStr">
+      <c r="V41" s="13" t="inlineStr">
         <is>
           <t>选款</t>
         </is>
       </c>
-      <c r="Z41" s="11" t="inlineStr">
+      <c r="W41" s="11" t="inlineStr">
         <is>
           <t>打分+定款</t>
         </is>
       </c>
-      <c r="AA41" s="10" t="inlineStr">
+      <c r="X41" s="10" t="inlineStr">
         <is>
           <t>SPU+作图</t>
         </is>
       </c>
-      <c r="AB41" s="10" t="inlineStr">
+      <c r="Y41" s="10" t="inlineStr">
         <is>
           <t>作图</t>
         </is>
       </c>
-      <c r="AC41" s="10" t="inlineStr">
-        <is>
-          <t>作图</t>
-        </is>
-      </c>
-      <c r="AD41" s="7" t="inlineStr">
-        <is>
-          <t>上架25</t>
-        </is>
-      </c>
+      <c r="Z41" s="7" t="inlineStr">
+        <is>
+          <t>上架10</t>
+        </is>
+      </c>
+      <c r="AA41" s="7" t="inlineStr">
+        <is>
+          <t>上架10</t>
+        </is>
+      </c>
+      <c r="AB41" s="7" t="inlineStr">
+        <is>
+          <t>上架10</t>
+        </is>
+      </c>
+      <c r="AC41" s="7" t="inlineStr">
+        <is>
+          <t>上架10</t>
+        </is>
+      </c>
+      <c r="AD41" s="5" t="inlineStr"/>
       <c r="AE41" s="8" t="inlineStr">
         <is>
           <t>假期</t>
@@ -5476,31 +5581,24 @@
           <t>假期</t>
         </is>
       </c>
-      <c r="AG41" s="7" t="inlineStr">
-        <is>
-          <t>上架25</t>
-        </is>
-      </c>
+      <c r="AG41" s="5" t="inlineStr"/>
       <c r="AH41" s="5" t="inlineStr"/>
-      <c r="AI41" s="3" t="inlineStr">
-        <is>
-          <t>复杂品类(60%+单个作图), 作图排3周</t>
-        </is>
-      </c>
+      <c r="AI41" s="3" t="inlineStr"/>
+      <c r="AJ41" s="3" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>晚礼服 Evening</t>
+          <t>舞会裙 Prom</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>2027-02 批</t>
+          <t>2027-01 批</t>
         </is>
       </c>
       <c r="C42" s="5" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D42" s="5" t="inlineStr"/>
       <c r="E42" s="5" t="inlineStr"/>
@@ -5519,36 +5617,52 @@
       <c r="R42" s="5" t="inlineStr"/>
       <c r="S42" s="5" t="inlineStr"/>
       <c r="T42" s="5" t="inlineStr"/>
-      <c r="U42" s="5" t="inlineStr"/>
-      <c r="V42" s="5" t="inlineStr"/>
-      <c r="W42" s="5" t="inlineStr"/>
-      <c r="X42" s="5" t="inlineStr"/>
-      <c r="Y42" s="5" t="inlineStr"/>
-      <c r="Z42" s="12" t="inlineStr">
+      <c r="U42" s="13" t="inlineStr">
         <is>
           <t>选款</t>
         </is>
       </c>
-      <c r="AA42" s="11" t="inlineStr">
+      <c r="V42" s="11" t="inlineStr">
         <is>
           <t>打分+定款</t>
         </is>
       </c>
-      <c r="AB42" s="10" t="inlineStr">
-        <is>
-          <t>SPU+作图</t>
-        </is>
-      </c>
-      <c r="AC42" s="10" t="inlineStr">
+      <c r="W42" s="14" t="inlineStr">
+        <is>
+          <t>SPU</t>
+        </is>
+      </c>
+      <c r="X42" s="10" t="inlineStr">
         <is>
           <t>作图</t>
         </is>
       </c>
-      <c r="AD42" s="7" t="inlineStr">
-        <is>
-          <t>上架15</t>
-        </is>
-      </c>
+      <c r="Y42" s="10" t="inlineStr">
+        <is>
+          <t>作图</t>
+        </is>
+      </c>
+      <c r="Z42" s="7" t="inlineStr">
+        <is>
+          <t>上架10</t>
+        </is>
+      </c>
+      <c r="AA42" s="7" t="inlineStr">
+        <is>
+          <t>上架10</t>
+        </is>
+      </c>
+      <c r="AB42" s="7" t="inlineStr">
+        <is>
+          <t>上架10</t>
+        </is>
+      </c>
+      <c r="AC42" s="7" t="inlineStr">
+        <is>
+          <t>上架10</t>
+        </is>
+      </c>
+      <c r="AD42" s="5" t="inlineStr"/>
       <c r="AE42" s="8" t="inlineStr">
         <is>
           <t>假期</t>
@@ -5559,27 +5673,28 @@
           <t>假期</t>
         </is>
       </c>
-      <c r="AG42" s="7" t="inlineStr">
-        <is>
-          <t>上架15</t>
-        </is>
-      </c>
+      <c r="AG42" s="5" t="inlineStr"/>
       <c r="AH42" s="5" t="inlineStr"/>
       <c r="AI42" s="3" t="inlineStr"/>
+      <c r="AJ42" s="3" t="inlineStr">
+        <is>
+          <t>选款提前至前5周, 与ED/BD错峰</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>婚纱 Bride</t>
+          <t>鸡尾酒裙 Cocktail</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>2027-02 批</t>
+          <t>2027-01 批</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D43" s="5" t="inlineStr"/>
       <c r="E43" s="5" t="inlineStr"/>
@@ -5600,30 +5715,38 @@
       <c r="T43" s="5" t="inlineStr"/>
       <c r="U43" s="5" t="inlineStr"/>
       <c r="V43" s="5" t="inlineStr"/>
-      <c r="W43" s="5" t="inlineStr"/>
-      <c r="X43" s="5" t="inlineStr"/>
-      <c r="Y43" s="5" t="inlineStr"/>
-      <c r="Z43" s="5" t="inlineStr"/>
-      <c r="AA43" s="11" t="inlineStr">
-        <is>
-          <t>选款+打分+定款</t>
-        </is>
-      </c>
-      <c r="AB43" s="10" t="inlineStr">
+      <c r="W43" s="13" t="inlineStr">
+        <is>
+          <t>选款</t>
+        </is>
+      </c>
+      <c r="X43" s="11" t="inlineStr">
+        <is>
+          <t>打分+定款</t>
+        </is>
+      </c>
+      <c r="Y43" s="10" t="inlineStr">
         <is>
           <t>SPU+作图</t>
         </is>
       </c>
-      <c r="AC43" s="10" t="inlineStr">
+      <c r="Z43" s="10" t="inlineStr">
         <is>
           <t>作图</t>
         </is>
       </c>
-      <c r="AD43" s="7" t="inlineStr">
-        <is>
-          <t>上架10</t>
-        </is>
-      </c>
+      <c r="AA43" s="7" t="inlineStr">
+        <is>
+          <t>上架15</t>
+        </is>
+      </c>
+      <c r="AB43" s="7" t="inlineStr">
+        <is>
+          <t>上架15</t>
+        </is>
+      </c>
+      <c r="AC43" s="5" t="inlineStr"/>
+      <c r="AD43" s="5" t="inlineStr"/>
       <c r="AE43" s="8" t="inlineStr">
         <is>
           <t>假期</t>
@@ -5636,25 +5759,26 @@
       </c>
       <c r="AG43" s="5" t="inlineStr"/>
       <c r="AH43" s="5" t="inlineStr"/>
-      <c r="AI43" s="3" t="inlineStr">
-        <is>
-          <t>小批次: 选款打分同周合并, 可走直接定款再压缩1周</t>
+      <c r="AI43" s="3" t="inlineStr"/>
+      <c r="AJ43" s="3" t="inlineStr">
+        <is>
+          <t>按首个上架周(1/11)前4周选款, 避开12/7选款高峰</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>伴娘裙 Bridesmaid</t>
+          <t>花童裙 Flower Girl</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>2027-02 批</t>
+          <t>2027-01 批</t>
         </is>
       </c>
       <c r="C44" s="5" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D44" s="5" t="inlineStr"/>
       <c r="E44" s="5" t="inlineStr"/>
@@ -5678,48 +5802,369 @@
       <c r="W44" s="5" t="inlineStr"/>
       <c r="X44" s="5" t="inlineStr"/>
       <c r="Y44" s="5" t="inlineStr"/>
-      <c r="Z44" s="12" t="inlineStr">
+      <c r="Z44" s="11" t="inlineStr">
+        <is>
+          <t>选款+打分+定款</t>
+        </is>
+      </c>
+      <c r="AA44" s="10" t="inlineStr">
+        <is>
+          <t>SPU+作图</t>
+        </is>
+      </c>
+      <c r="AB44" s="10" t="inlineStr">
+        <is>
+          <t>作图</t>
+        </is>
+      </c>
+      <c r="AC44" s="7" t="inlineStr">
+        <is>
+          <t>上架20</t>
+        </is>
+      </c>
+      <c r="AD44" s="5" t="inlineStr"/>
+      <c r="AE44" s="8" t="inlineStr">
+        <is>
+          <t>假期</t>
+        </is>
+      </c>
+      <c r="AF44" s="8" t="inlineStr">
+        <is>
+          <t>假期</t>
+        </is>
+      </c>
+      <c r="AG44" s="5" t="inlineStr"/>
+      <c r="AH44" s="5" t="inlineStr"/>
+      <c r="AI44" s="12" t="inlineStr">
+        <is>
+          <t>定款周(1/4)与ED/BD 2月批选款撞期, 建议直接定款</t>
+        </is>
+      </c>
+      <c r="AJ44" s="3" t="inlineStr">
+        <is>
+          <t>小批次: 选款打分同周合并</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>妈妈装 Mother of the Bride</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>2027-02 批</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D45" s="5" t="inlineStr"/>
+      <c r="E45" s="5" t="inlineStr"/>
+      <c r="F45" s="5" t="inlineStr"/>
+      <c r="G45" s="5" t="inlineStr"/>
+      <c r="H45" s="5" t="inlineStr"/>
+      <c r="I45" s="5" t="inlineStr"/>
+      <c r="J45" s="5" t="inlineStr"/>
+      <c r="K45" s="5" t="inlineStr"/>
+      <c r="L45" s="5" t="inlineStr"/>
+      <c r="M45" s="5" t="inlineStr"/>
+      <c r="N45" s="5" t="inlineStr"/>
+      <c r="O45" s="5" t="inlineStr"/>
+      <c r="P45" s="5" t="inlineStr"/>
+      <c r="Q45" s="5" t="inlineStr"/>
+      <c r="R45" s="5" t="inlineStr"/>
+      <c r="S45" s="5" t="inlineStr"/>
+      <c r="T45" s="5" t="inlineStr"/>
+      <c r="U45" s="5" t="inlineStr"/>
+      <c r="V45" s="5" t="inlineStr"/>
+      <c r="W45" s="5" t="inlineStr"/>
+      <c r="X45" s="5" t="inlineStr"/>
+      <c r="Y45" s="13" t="inlineStr">
         <is>
           <t>选款</t>
         </is>
       </c>
-      <c r="AA44" s="11" t="inlineStr">
+      <c r="Z45" s="11" t="inlineStr">
         <is>
           <t>打分+定款</t>
         </is>
       </c>
-      <c r="AB44" s="10" t="inlineStr">
+      <c r="AA45" s="10" t="inlineStr">
         <is>
           <t>SPU+作图</t>
         </is>
       </c>
-      <c r="AC44" s="10" t="inlineStr">
+      <c r="AB45" s="10" t="inlineStr">
         <is>
           <t>作图</t>
         </is>
       </c>
-      <c r="AD44" s="7" t="inlineStr">
+      <c r="AC45" s="10" t="inlineStr">
+        <is>
+          <t>作图</t>
+        </is>
+      </c>
+      <c r="AD45" s="7" t="inlineStr">
+        <is>
+          <t>上架25</t>
+        </is>
+      </c>
+      <c r="AE45" s="8" t="inlineStr">
+        <is>
+          <t>假期</t>
+        </is>
+      </c>
+      <c r="AF45" s="8" t="inlineStr">
+        <is>
+          <t>假期</t>
+        </is>
+      </c>
+      <c r="AG45" s="7" t="inlineStr">
+        <is>
+          <t>上架25</t>
+        </is>
+      </c>
+      <c r="AH45" s="5" t="inlineStr"/>
+      <c r="AI45" s="3" t="inlineStr"/>
+      <c r="AJ45" s="3" t="inlineStr">
+        <is>
+          <t>复杂品类(60%+单个作图), 作图排3周</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>晚礼服 Evening</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>2027-02 批</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="D46" s="5" t="inlineStr"/>
+      <c r="E46" s="5" t="inlineStr"/>
+      <c r="F46" s="5" t="inlineStr"/>
+      <c r="G46" s="5" t="inlineStr"/>
+      <c r="H46" s="5" t="inlineStr"/>
+      <c r="I46" s="5" t="inlineStr"/>
+      <c r="J46" s="5" t="inlineStr"/>
+      <c r="K46" s="5" t="inlineStr"/>
+      <c r="L46" s="5" t="inlineStr"/>
+      <c r="M46" s="5" t="inlineStr"/>
+      <c r="N46" s="5" t="inlineStr"/>
+      <c r="O46" s="5" t="inlineStr"/>
+      <c r="P46" s="5" t="inlineStr"/>
+      <c r="Q46" s="5" t="inlineStr"/>
+      <c r="R46" s="5" t="inlineStr"/>
+      <c r="S46" s="5" t="inlineStr"/>
+      <c r="T46" s="5" t="inlineStr"/>
+      <c r="U46" s="5" t="inlineStr"/>
+      <c r="V46" s="5" t="inlineStr"/>
+      <c r="W46" s="5" t="inlineStr"/>
+      <c r="X46" s="5" t="inlineStr"/>
+      <c r="Y46" s="5" t="inlineStr"/>
+      <c r="Z46" s="13" t="inlineStr">
+        <is>
+          <t>选款</t>
+        </is>
+      </c>
+      <c r="AA46" s="11" t="inlineStr">
+        <is>
+          <t>打分+定款</t>
+        </is>
+      </c>
+      <c r="AB46" s="10" t="inlineStr">
+        <is>
+          <t>SPU+作图</t>
+        </is>
+      </c>
+      <c r="AC46" s="10" t="inlineStr">
+        <is>
+          <t>作图</t>
+        </is>
+      </c>
+      <c r="AD46" s="7" t="inlineStr">
         <is>
           <t>上架15</t>
         </is>
       </c>
-      <c r="AE44" s="8" t="inlineStr">
-        <is>
-          <t>假期</t>
-        </is>
-      </c>
-      <c r="AF44" s="8" t="inlineStr">
-        <is>
-          <t>假期</t>
-        </is>
-      </c>
-      <c r="AG44" s="7" t="inlineStr">
+      <c r="AE46" s="8" t="inlineStr">
+        <is>
+          <t>假期</t>
+        </is>
+      </c>
+      <c r="AF46" s="8" t="inlineStr">
+        <is>
+          <t>假期</t>
+        </is>
+      </c>
+      <c r="AG46" s="7" t="inlineStr">
         <is>
           <t>上架15</t>
         </is>
       </c>
-      <c r="AH44" s="5" t="inlineStr"/>
-      <c r="AI44" s="3" t="inlineStr"/>
+      <c r="AH46" s="5" t="inlineStr"/>
+      <c r="AI46" s="3" t="inlineStr"/>
+      <c r="AJ46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>婚纱 Bride(来图定制)</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>2027-02 批</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D47" s="5" t="inlineStr"/>
+      <c r="E47" s="5" t="inlineStr"/>
+      <c r="F47" s="5" t="inlineStr"/>
+      <c r="G47" s="5" t="inlineStr"/>
+      <c r="H47" s="5" t="inlineStr"/>
+      <c r="I47" s="5" t="inlineStr"/>
+      <c r="J47" s="5" t="inlineStr"/>
+      <c r="K47" s="5" t="inlineStr"/>
+      <c r="L47" s="5" t="inlineStr"/>
+      <c r="M47" s="5" t="inlineStr"/>
+      <c r="N47" s="5" t="inlineStr"/>
+      <c r="O47" s="5" t="inlineStr"/>
+      <c r="P47" s="5" t="inlineStr"/>
+      <c r="Q47" s="5" t="inlineStr"/>
+      <c r="R47" s="5" t="inlineStr"/>
+      <c r="S47" s="5" t="inlineStr"/>
+      <c r="T47" s="5" t="inlineStr"/>
+      <c r="U47" s="5" t="inlineStr"/>
+      <c r="V47" s="5" t="inlineStr"/>
+      <c r="W47" s="5" t="inlineStr"/>
+      <c r="X47" s="5" t="inlineStr"/>
+      <c r="Y47" s="5" t="inlineStr"/>
+      <c r="Z47" s="5" t="inlineStr"/>
+      <c r="AA47" s="5" t="inlineStr"/>
+      <c r="AB47" s="10" t="inlineStr">
+        <is>
+          <t>SPU+作图</t>
+        </is>
+      </c>
+      <c r="AC47" s="10" t="inlineStr">
+        <is>
+          <t>作图</t>
+        </is>
+      </c>
+      <c r="AD47" s="7" t="inlineStr">
+        <is>
+          <t>上架10</t>
+        </is>
+      </c>
+      <c r="AE47" s="8" t="inlineStr">
+        <is>
+          <t>假期</t>
+        </is>
+      </c>
+      <c r="AF47" s="8" t="inlineStr">
+        <is>
+          <t>假期</t>
+        </is>
+      </c>
+      <c r="AG47" s="5" t="inlineStr"/>
+      <c r="AH47" s="5" t="inlineStr"/>
+      <c r="AI47" s="3" t="inlineStr"/>
+      <c r="AJ47" s="3" t="inlineStr">
+        <is>
+          <t>来图定制来源(月供约20款), 无需选款打分定款</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>伴娘裙 Bridesmaid</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>2027-02 批</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="D48" s="5" t="inlineStr"/>
+      <c r="E48" s="5" t="inlineStr"/>
+      <c r="F48" s="5" t="inlineStr"/>
+      <c r="G48" s="5" t="inlineStr"/>
+      <c r="H48" s="5" t="inlineStr"/>
+      <c r="I48" s="5" t="inlineStr"/>
+      <c r="J48" s="5" t="inlineStr"/>
+      <c r="K48" s="5" t="inlineStr"/>
+      <c r="L48" s="5" t="inlineStr"/>
+      <c r="M48" s="5" t="inlineStr"/>
+      <c r="N48" s="5" t="inlineStr"/>
+      <c r="O48" s="5" t="inlineStr"/>
+      <c r="P48" s="5" t="inlineStr"/>
+      <c r="Q48" s="5" t="inlineStr"/>
+      <c r="R48" s="5" t="inlineStr"/>
+      <c r="S48" s="5" t="inlineStr"/>
+      <c r="T48" s="5" t="inlineStr"/>
+      <c r="U48" s="5" t="inlineStr"/>
+      <c r="V48" s="5" t="inlineStr"/>
+      <c r="W48" s="5" t="inlineStr"/>
+      <c r="X48" s="5" t="inlineStr"/>
+      <c r="Y48" s="5" t="inlineStr"/>
+      <c r="Z48" s="13" t="inlineStr">
+        <is>
+          <t>选款</t>
+        </is>
+      </c>
+      <c r="AA48" s="11" t="inlineStr">
+        <is>
+          <t>打分+定款</t>
+        </is>
+      </c>
+      <c r="AB48" s="10" t="inlineStr">
+        <is>
+          <t>SPU+作图</t>
+        </is>
+      </c>
+      <c r="AC48" s="10" t="inlineStr">
+        <is>
+          <t>作图</t>
+        </is>
+      </c>
+      <c r="AD48" s="7" t="inlineStr">
+        <is>
+          <t>上架15</t>
+        </is>
+      </c>
+      <c r="AE48" s="8" t="inlineStr">
+        <is>
+          <t>假期</t>
+        </is>
+      </c>
+      <c r="AF48" s="8" t="inlineStr">
+        <is>
+          <t>假期</t>
+        </is>
+      </c>
+      <c r="AG48" s="7" t="inlineStr">
+        <is>
+          <t>上架15</t>
+        </is>
+      </c>
+      <c r="AH48" s="5" t="inlineStr"/>
+      <c r="AI48" s="3" t="inlineStr"/>
+      <c r="AJ48" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5736,10 +6181,10 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="46" customWidth="1" min="8" max="8"/>
@@ -5795,12 +6240,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>婚纱2608批(50款)、妈妈装2609批(80款)、婚纱2609批(50款)</t>
+          <t>★婚纱2608批-选款(30款)、妈妈装2609批(80款)、婚纱2609批-选款(30款)</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>伴娘裙2608批(40款)、婚纱2608批(50款)</t>
+          <t>伴娘裙2608批(40款)、★婚纱2608批-选款(30款)</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -5817,7 +6262,7 @@
       <c r="G2" s="5" t="inlineStr"/>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>追赶周: WD 8月批紧急直接定款; 同时启动 MBD/WD 9月批选款</t>
+          <t>★=直接定款候选, 人力排不开时由负责人直接定款; 追赶周: WD 8月批直接定款30款; 同时启动 MBD/WD 9月批选款</t>
         </is>
       </c>
     </row>
@@ -5829,22 +6274,22 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>晚礼服2609批(40款)、伴娘裙2609批(40款)、花童裙2609批(30款)</t>
+          <t>晚礼服2609批(40款)、伴娘裙2609批(40款)、★花童裙2609批(30款)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>妈妈装2609批(80款)、婚纱2609批(50款)</t>
+          <t>妈妈装2609批(80款)、婚纱2609批-选款(30款)</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>伴娘裙2608批(40款)、婚纱2608批(50款)</t>
+          <t>伴娘裙2608批(40款)、★婚纱2608批-选款(30款)、婚纱2608批-来图定制(20款)</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>妈妈装2608批(70款)、晚礼服2608批(40款)、伴娘裙2608批(40款)、婚纱2608批(50款)</t>
+          <t>妈妈装2608批(70款)、晚礼服2608批(40款)、伴娘裙2608批(40款)、★婚纱2608批-选款(30款)、婚纱2608批-来图定制(20款)</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -5855,7 +6300,11 @@
       <c r="G3" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>★=直接定款候选, 人力排不开时由负责人直接定款</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -5866,17 +6315,17 @@
       <c r="B4" s="3" t="inlineStr"/>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>晚礼服2609批(40款)、伴娘裙2609批(40款)、花童裙2609批(30款)</t>
+          <t>晚礼服2609批(40款)、伴娘裙2609批(40款)、★花童裙2609批(30款)</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>妈妈装2609批(80款)、婚纱2609批(50款)</t>
+          <t>妈妈装2609批(80款)、婚纱2609批-选款(30款)</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>伴娘裙2608批(40款)、婚纱2608批(50款)、妈妈装2609批(80款)、婚纱2609批(50款)</t>
+          <t>伴娘裙2608批(40款)、★婚纱2608批-选款(30款)、婚纱2608批-来图定制(20款)、妈妈装2609批(80款)、婚纱2609批-选款(30款)</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -5887,7 +6336,11 @@
       <c r="G4" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>★=直接定款候选, 人力排不开时由负责人直接定款</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -5895,33 +6348,25 @@
           <t>8/24周 (8.24-8.28)</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>鸡尾酒裙2609批(20款)</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>鸡尾酒裙2609批(20款)</t>
-        </is>
-      </c>
+      <c r="B5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>晚礼服2609批(40款)、伴娘裙2609批(40款)、花童裙2609批(30款)</t>
+          <t>晚礼服2609批(40款)、伴娘裙2609批(40款)、婚纱2609批-来图定制(20款)、★花童裙2609批(30款)</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>婚纱2608批(50款)、妈妈装2609批(80款)、晚礼服2609批(40款)、婚纱2609批(50款)、伴娘裙2609批(40款)、花童裙2609批(30款)</t>
+          <t>★婚纱2608批-选款(30款)、妈妈装2609批(80款)、晚礼服2609批(40款)、伴娘裙2609批(40款)、婚纱2609批-选款(30款)、婚纱2609批-来图定制(20款)、★花童裙2609批(30款)</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>妈妈装 15款、晚礼服 15款、伴娘裙 20款、婚纱 15款</t>
+          <t>妈妈装 15款、晚礼服 15款、伴娘裙 20款、婚纱 20款</t>
         </is>
       </c>
       <c r="G5" s="5" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H5" s="3" t="inlineStr"/>
     </row>
@@ -5933,7 +6378,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>妈妈装2610批(80款)、婚纱2610批(40款)</t>
+          <t>妈妈装2610批(80款)、婚纱2610批-选款(20款)</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
@@ -5944,16 +6389,16 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>妈妈装2609批(80款)、晚礼服2609批(40款)、婚纱2609批(50款)、伴娘裙2609批(40款)、鸡尾酒裙2609批(20款)、花童裙2609批(30款)</t>
+          <t>妈妈装2609批(80款)、晚礼服2609批(40款)、伴娘裙2609批(40款)、婚纱2609批-选款(30款)、婚纱2609批-来图定制(20款)、鸡尾酒裙2609批(20款)、★花童裙2609批(30款)</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>妈妈装 15款、晚礼服 10款、伴娘裙 20款、婚纱 35款</t>
+          <t>妈妈装 15款、晚礼服 10款、伴娘裙 20款、婚纱 30款</t>
         </is>
       </c>
       <c r="G6" s="5" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H6" s="3" t="inlineStr"/>
     </row>
@@ -5965,12 +6410,12 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>晚礼服2610批(40款)、伴娘裙2610批(40款)、小伴娘裙2610批(30款)</t>
+          <t>晚礼服2610批(40款)、伴娘裙2610批(40款)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>妈妈装2610批(80款)、婚纱2610批(40款)</t>
+          <t>妈妈装2610批(80款)、婚纱2610批-选款(20款)</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr"/>
@@ -5981,7 +6426,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>妈妈装 20款、晚礼服 10款、婚纱 13款、伴娘裙 10款、花童裙 15款</t>
+          <t>妈妈装 20款、晚礼服 10款、伴娘裙 10款、婚纱 8款、婚纱 5款、花童裙 15款</t>
         </is>
       </c>
       <c r="G7" s="5" t="n">
@@ -5998,22 +6443,22 @@
       <c r="B8" s="3" t="inlineStr"/>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>晚礼服2610批(40款)、伴娘裙2610批(40款)、小伴娘裙2610批(30款)</t>
+          <t>晚礼服2610批(40款)、伴娘裙2610批(40款)</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>妈妈装2610批(80款)、婚纱2610批(40款)</t>
+          <t>妈妈装2610批(80款)、婚纱2610批-选款(20款)</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>妈妈装2610批(80款)、婚纱2610批(40款)</t>
+          <t>妈妈装2610批(80款)、婚纱2610批-选款(20款)</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>妈妈装 20款、晚礼服 10款、婚纱 13款、伴娘裙 10款、鸡尾酒裙 20款</t>
+          <t>妈妈装 20款、晚礼服 10款、伴娘裙 10款、婚纱 8款、婚纱 5款、鸡尾酒裙 20款</t>
         </is>
       </c>
       <c r="G8" s="5" t="n">
@@ -6039,17 +6484,17 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>晚礼服2610批(40款)、伴娘裙2610批(40款)、小伴娘裙2610批(30款)</t>
+          <t>晚礼服2610批(40款)、伴娘裙2610批(40款)、婚纱2610批-来图定制(20款)、小伴娘裙2610批(30款)</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>妈妈装2610批(80款)、晚礼服2610批(40款)、婚纱2610批(40款)、伴娘裙2610批(40款)、小伴娘裙2610批(30款)</t>
+          <t>妈妈装2610批(80款)、晚礼服2610批(40款)、伴娘裙2610批(40款)、婚纱2610批-选款(20款)、婚纱2610批-来图定制(20款)、小伴娘裙2610批(30款)</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>妈妈装 20款、晚礼服 10款、婚纱 12款、伴娘裙 10款、花童裙 15款</t>
+          <t>妈妈装 20款、晚礼服 10款、伴娘裙 10款、婚纱 7款、婚纱 5款、花童裙 15款</t>
         </is>
       </c>
       <c r="G9" s="5" t="n">
@@ -6065,7 +6510,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>妈妈装2611批(100款)、婚纱2611批(40款)</t>
+          <t>妈妈装2611批(100款)、婚纱2611批-选款(20款)</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr"/>
@@ -6076,12 +6521,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>妈妈装2610批(80款)、晚礼服2610批(40款)、婚纱2610批(40款)、伴娘裙2610批(40款)、鸡尾酒裙2610批(10款)、小伴娘裙2610批(30款)</t>
+          <t>妈妈装2610批(80款)、晚礼服2610批(40款)、伴娘裙2610批(40款)、婚纱2610批-选款(20款)、婚纱2610批-来图定制(20款)、鸡尾酒裙2610批(10款)、小伴娘裙2610批(30款)</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>妈妈装 20款、晚礼服 10款、婚纱 12款、伴娘裙 10款</t>
+          <t>妈妈装 20款、晚礼服 10款、伴娘裙 10款、婚纱 7款、婚纱 5款</t>
         </is>
       </c>
       <c r="G10" s="5" t="n">
@@ -6097,12 +6542,12 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>花童裙2610批(20款)、晚礼服2611批(60款)、伴娘裙2611批(50款)</t>
+          <t>晚礼服2611批(60款)、伴娘裙2611批(50款)、★花童裙2610批(20款)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>花童裙2610批(20款)、妈妈装2611批(100款)、婚纱2611批(40款)</t>
+          <t>妈妈装2611批(100款)、婚纱2611批-选款(20款)、★花童裙2610批(20款)</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr"/>
@@ -6113,13 +6558,17 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>妈妈装 20款、晚礼服 10款、婚纱 10款、伴娘裙 10款、小伴娘裙 15款</t>
+          <t>妈妈装 20款、晚礼服 10款、伴娘裙 10款、婚纱 5款、婚纱 5款、小伴娘裙 15款</t>
         </is>
       </c>
       <c r="G11" s="5" t="n">
         <v>65</v>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>★=直接定款候选, 人力排不开时由负责人直接定款</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -6135,17 +6584,17 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>花童裙2610批(20款)、妈妈装2611批(100款)、婚纱2611批(40款)</t>
+          <t>妈妈装2611批(100款)、婚纱2611批-选款(20款)、★花童裙2610批(20款)</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>花童裙2610批(20款)、妈妈装2611批(100款)、婚纱2611批(40款)</t>
+          <t>妈妈装2611批(100款)、婚纱2611批-选款(20款)、★花童裙2610批(20款)</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>妈妈装 20款、晚礼服 10款、婚纱 10款、伴娘裙 10款、鸡尾酒裙 10款</t>
+          <t>妈妈装 20款、晚礼服 10款、伴娘裙 10款、婚纱 5款、婚纱 5款、鸡尾酒裙 10款</t>
         </is>
       </c>
       <c r="G12" s="5" t="n">
@@ -6171,17 +6620,17 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>晚礼服2611批(60款)、伴娘裙2611批(50款)</t>
+          <t>晚礼服2611批(60款)、伴娘裙2611批(50款)、婚纱2611批-来图定制(20款)</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>花童裙2610批(20款)、妈妈装2611批(100款)、晚礼服2611批(60款)、婚纱2611批(40款)、伴娘裙2611批(50款)</t>
+          <t>妈妈装2611批(100款)、晚礼服2611批(60款)、伴娘裙2611批(50款)、婚纱2611批-选款(20款)、婚纱2611批-来图定制(20款)、★花童裙2610批(20款)</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>妈妈装 20款、晚礼服 10款、婚纱 10款、伴娘裙 10款、小伴娘裙 15款</t>
+          <t>妈妈装 20款、晚礼服 10款、伴娘裙 10款、婚纱 5款、婚纱 5款、小伴娘裙 15款</t>
         </is>
       </c>
       <c r="G13" s="5" t="n">
@@ -6212,12 +6661,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>妈妈装2611批(100款)、晚礼服2611批(60款)、婚纱2611批(40款)、伴娘裙2611批(50款)、舞会裙2611批(20款)</t>
+          <t>妈妈装2611批(100款)、晚礼服2611批(60款)、伴娘裙2611批(50款)、婚纱2611批-选款(20款)、婚纱2611批-来图定制(20款)、舞会裙2611批(20款)</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>妈妈装 20款、晚礼服 10款、婚纱 10款、伴娘裙 10款、花童裙 20款</t>
+          <t>妈妈装 20款、晚礼服 10款、伴娘裙 10款、婚纱 5款、婚纱 5款、花童裙 20款</t>
         </is>
       </c>
       <c r="G14" s="5" t="n">
@@ -6233,12 +6682,12 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>花童裙2611批(10款)、妈妈装2612批(80款)</t>
+          <t>妈妈装2612批(80款)、舞会裙2612批(40款)、★花童裙2611批(10款)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>花童裙2611批(10款)</t>
+          <t>★花童裙2611批(10款)</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -6253,13 +6702,17 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>妈妈装 20款、晚礼服 12款、婚纱 8款、伴娘裙 10款</t>
+          <t>妈妈装 20款、晚礼服 12款、伴娘裙 10款、婚纱 4款、婚纱 4款</t>
         </is>
       </c>
       <c r="G15" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="H15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>★=直接定款候选, 人力排不开时由负责人直接定款</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -6269,27 +6722,27 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>晚礼服2612批(50款)、伴娘裙2612批(40款)、舞会裙2612批(40款)</t>
+          <t>晚礼服2612批(50款)、伴娘裙2612批(40款)</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>妈妈装2612批(80款)</t>
+          <t>妈妈装2612批(80款)、舞会裙2612批(40款)</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>花童裙2611批(10款)</t>
+          <t>★花童裙2611批(10款)</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>鸡尾酒裙2611批(20款)、花童裙2611批(10款)</t>
+          <t>鸡尾酒裙2611批(20款)、★花童裙2611批(10款)</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>妈妈装 20款、晚礼服 12款、婚纱 8款、伴娘裙 10款、舞会裙 20款</t>
+          <t>妈妈装 20款、晚礼服 12款、伴娘裙 10款、婚纱 4款、婚纱 4款、舞会裙 20款</t>
         </is>
       </c>
       <c r="G16" s="5" t="n">
@@ -6310,22 +6763,22 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>晚礼服2612批(50款)、伴娘裙2612批(40款)、舞会裙2612批(40款)、鸡尾酒裙2612批(20款)</t>
+          <t>晚礼服2612批(50款)、伴娘裙2612批(40款)、鸡尾酒裙2612批(20款)</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>妈妈装2612批(80款)</t>
+          <t>妈妈装2612批(80款)、舞会裙2612批(40款)</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>花童裙2611批(10款)、妈妈装2612批(80款)</t>
+          <t>妈妈装2612批(80款)、★花童裙2611批(10款)</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>妈妈装 20款、晚礼服 12款、婚纱 8款、伴娘裙 10款、鸡尾酒裙 20款</t>
+          <t>妈妈装 20款、晚礼服 12款、伴娘裙 10款、婚纱 4款、婚纱 4款、鸡尾酒裙 20款</t>
         </is>
       </c>
       <c r="G17" s="5" t="n">
@@ -6339,19 +6792,11 @@
           <t>11/23周 (11.23-11.27)</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>婚纱2612批(10款)</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>婚纱2612批(10款)</t>
-        </is>
-      </c>
+      <c r="B18" s="3" t="inlineStr"/>
+      <c r="C18" s="3" t="inlineStr"/>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>晚礼服2612批(50款)、伴娘裙2612批(40款)、舞会裙2612批(40款)、鸡尾酒裙2612批(20款)</t>
+          <t>晚礼服2612批(50款)、伴娘裙2612批(40款)、鸡尾酒裙2612批(20款)</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -6361,7 +6806,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>妈妈装 20款、晚礼服 12款、婚纱 8款、伴娘裙 10款、花童裙 10款</t>
+          <t>妈妈装 20款、晚礼服 12款、伴娘裙 10款、婚纱 4款、婚纱 4款、花童裙 10款</t>
         </is>
       </c>
       <c r="G18" s="5" t="n">
@@ -6377,33 +6822,37 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>花童裙2612批(20款)、妈妈装2701批(80款)</t>
+          <t>妈妈装2701批(80款)、舞会裙2701批(40款)、★花童裙2612批(20款)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>花童裙2612批(20款)</t>
+          <t>★花童裙2612批(20款)</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>婚纱2612批(10款)</t>
+          <t>婚纱2612批-来图定制(10款)</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>妈妈装2612批(80款)、晚礼服2612批(50款)、婚纱2612批(10款)、伴娘裙2612批(40款)、舞会裙2612批(40款)、鸡尾酒裙2612批(20款)</t>
+          <t>妈妈装2612批(80款)、晚礼服2612批(50款)、伴娘裙2612批(40款)、婚纱2612批-来图定制(10款)、舞会裙2612批(40款)、鸡尾酒裙2612批(20款)</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>妈妈装 20款、晚礼服 12款、婚纱 8款、伴娘裙 10款</t>
+          <t>妈妈装 20款、晚礼服 12款、伴娘裙 10款、婚纱 4款、婚纱 4款</t>
         </is>
       </c>
       <c r="G19" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="H19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>★=直接定款候选, 人力排不开时由负责人直接定款</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -6413,22 +6862,22 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>小伴娘裙2612批(20款)、晚礼服2701批(40款)、伴娘裙2701批(40款)、舞会裙2701批(40款)、鸡尾酒裙2701批(30款)</t>
+          <t>晚礼服2701批(40款)、伴娘裙2701批(40款)、★小伴娘裙2612批(20款)</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>小伴娘裙2612批(20款)、妈妈装2701批(80款)</t>
+          <t>妈妈装2701批(80款)、舞会裙2701批(40款)、★小伴娘裙2612批(20款)</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>花童裙2612批(20款)</t>
+          <t>★花童裙2612批(20款)</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>婚纱2612批(10款)、花童裙2612批(20款)</t>
+          <t>婚纱2612批-来图定制(10款)、★花童裙2612批(20款)</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -6439,7 +6888,11 @@
       <c r="G20" s="5" t="n">
         <v>73</v>
       </c>
-      <c r="H20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>★=直接定款候选, 人力排不开时由负责人直接定款</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
@@ -6447,25 +6900,29 @@
           <t>12/14周 (12.14-12.18)</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>鸡尾酒裙2701批(30款)</t>
+        </is>
+      </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>晚礼服2701批(40款)、伴娘裙2701批(40款)、舞会裙2701批(40款)、鸡尾酒裙2701批(30款)</t>
+          <t>晚礼服2701批(40款)、伴娘裙2701批(40款)</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>小伴娘裙2612批(20款)、妈妈装2701批(80款)</t>
+          <t>妈妈装2701批(80款)、舞会裙2701批(40款)、★小伴娘裙2612批(20款)</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>花童裙2612批(20款)、小伴娘裙2612批(20款)、妈妈装2701批(80款)</t>
+          <t>妈妈装2701批(80款)、★小伴娘裙2612批(20款)、★花童裙2612批(20款)</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>妈妈装 20款、晚礼服 13款、婚纱 10款、伴娘裙 10款、舞会裙 10款</t>
+          <t>妈妈装 20款、晚礼服 13款、伴娘裙 10款、婚纱 10款、舞会裙 10款</t>
         </is>
       </c>
       <c r="G21" s="5" t="n">
@@ -6479,24 +6936,20 @@
           <t>12/21周 (12.21-12.25)</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>婚纱2701批(10款)</t>
-        </is>
-      </c>
+      <c r="B22" s="3" t="inlineStr"/>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>婚纱2701批(10款)</t>
+          <t>鸡尾酒裙2701批(30款)</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>晚礼服2701批(40款)、伴娘裙2701批(40款)、舞会裙2701批(40款)、鸡尾酒裙2701批(30款)</t>
+          <t>晚礼服2701批(40款)、伴娘裙2701批(40款)、婚纱2701批-来图定制(10款)</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>小伴娘裙2612批(20款)、妈妈装2701批(80款)、晚礼服2701批(40款)、伴娘裙2701批(40款)、舞会裙2701批(40款)、鸡尾酒裙2701批(30款)</t>
+          <t>妈妈装2701批(80款)、晚礼服2701批(40款)、伴娘裙2701批(40款)、婚纱2701批-来图定制(10款)、舞会裙2701批(40款)、★小伴娘裙2612批(20款)</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -6523,12 +6976,12 @@
       <c r="C23" s="3" t="inlineStr"/>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>婚纱2701批(10款)</t>
+          <t>鸡尾酒裙2701批(30款)</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>妈妈装2701批(80款)、晚礼服2701批(40款)、婚纱2701批(10款)、伴娘裙2701批(40款)、舞会裙2701批(40款)、鸡尾酒裙2701批(30款)</t>
+          <t>妈妈装2701批(80款)、晚礼服2701批(40款)、伴娘裙2701批(40款)、婚纱2701批-来图定制(10款)、舞会裙2701批(40款)、鸡尾酒裙2701批(30款)</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -6549,29 +7002,33 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>花童裙2701批(20款)、晚礼服2702批(30款)、伴娘裙2702批(30款)</t>
+          <t>晚礼服2702批(30款)、伴娘裙2702批(30款)、★花童裙2701批(20款)</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>花童裙2701批(20款)、妈妈装2702批(50款)</t>
+          <t>妈妈装2702批(50款)、★花童裙2701批(20款)</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr"/>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>婚纱2701批(10款)</t>
+          <t>鸡尾酒裙2701批(30款)</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>妈妈装 20款、晚礼服 10款、伴娘裙 10款、舞会裙 10款、鸡尾酒裙 15款</t>
+          <t>妈妈装 20款、晚礼服 10款、伴娘裙 10款、婚纱 10款、舞会裙 10款</t>
         </is>
       </c>
       <c r="G24" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="H24" s="3" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>★=直接定款候选, 人力排不开时由负责人直接定款</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
@@ -6579,33 +7036,29 @@
           <t>1/11周 (1.11-1.15)</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>婚纱2702批(10款)</t>
-        </is>
-      </c>
+      <c r="B25" s="3" t="inlineStr"/>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>晚礼服2702批(30款)、婚纱2702批(10款)、伴娘裙2702批(30款)</t>
+          <t>晚礼服2702批(30款)、伴娘裙2702批(30款)</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>花童裙2701批(20款)、妈妈装2702批(50款)</t>
+          <t>妈妈装2702批(50款)、★花童裙2701批(20款)</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>花童裙2701批(20款)、妈妈装2702批(50款)</t>
+          <t>妈妈装2702批(50款)、★花童裙2701批(20款)</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>妈妈装 20款、晚礼服 10款、婚纱 10款、伴娘裙 10款、舞会裙 10款</t>
+          <t>妈妈装 20款、晚礼服 10款、伴娘裙 10款、舞会裙 10款、鸡尾酒裙 15款</t>
         </is>
       </c>
       <c r="G25" s="5" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H25" s="3" t="inlineStr"/>
     </row>
@@ -6619,12 +7072,12 @@
       <c r="C26" s="3" t="inlineStr"/>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>晚礼服2702批(30款)、婚纱2702批(10款)、伴娘裙2702批(30款)</t>
+          <t>晚礼服2702批(30款)、伴娘裙2702批(30款)、婚纱2702批-来图定制(10款)</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>花童裙2701批(20款)、妈妈装2702批(50款)、晚礼服2702批(30款)、婚纱2702批(10款)、伴娘裙2702批(30款)</t>
+          <t>妈妈装2702批(50款)、晚礼服2702批(30款)、伴娘裙2702批(30款)、婚纱2702批-来图定制(10款)、★花童裙2701批(20款)</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -6648,7 +7101,7 @@
       <c r="D27" s="3" t="inlineStr"/>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>妈妈装2702批(50款)、晚礼服2702批(30款)、婚纱2702批(10款)、伴娘裙2702批(30款)</t>
+          <t>妈妈装2702批(50款)、晚礼服2702批(30款)、伴娘裙2702批(30款)、婚纱2702批-来图定制(10款)</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -6661,7 +7114,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>节前最后完整周: 确认2月批次作图全部完成; 启动3月批次(MBD/WD)选款</t>
+          <t>节前最后完整周: 确认2月批次作图全部完成; 启动3月批次(MBD)选款</t>
         </is>
       </c>
     </row>
@@ -6677,7 +7130,7 @@
       <c r="E28" s="3" t="inlineStr"/>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>妈妈装 25款、晚礼服 15款、婚纱 10款、伴娘裙 15款</t>
+          <t>妈妈装 25款、晚礼服 15款、伴娘裙 15款、婚纱 10款</t>
         </is>
       </c>
       <c r="G28" s="5" t="n">
@@ -6774,11 +7227,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -6855,14 +7308,20 @@
       <c r="C2" s="5" t="n">
         <v>70</v>
       </c>
-      <c r="D2" s="5" t="n">
-        <v>105</v>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>2.6</v>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
@@ -6893,14 +7352,20 @@
       <c r="C3" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="D3" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>1.5</v>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
@@ -6925,20 +7390,20 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>婚纱 Bride</t>
+          <t>婚纱 Bride(选款)</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
@@ -6946,10 +7411,10 @@
         </is>
       </c>
       <c r="H4" s="5" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J4" s="5" t="n">
         <v>3</v>
@@ -6963,31 +7428,41 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>伴娘裙 Bridesmaid</t>
+          <t>婚纱 Bride(来图定制)</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>1.5</v>
+        <v>20</v>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="I5" s="5" t="n">
-        <v>28</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J5" s="5" t="n">
         <v>2</v>
@@ -6996,39 +7471,39 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>2026-09 批</t>
+          <t>2026-08 批</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>妈妈装 Mother of the Bride</t>
+          <t>伴娘裙 Bridesmaid</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>40</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -7039,34 +7514,34 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>晚礼服 Evening</t>
+          <t>妈妈装 Mother of the Bride</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>40</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -7077,34 +7552,34 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>婚纱 Bride</t>
+          <t>晚礼服 Evening</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>40</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -7115,34 +7590,34 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>伴娘裙 Bridesmaid</t>
+          <t>婚纱 Bride(选款)</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="I9" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I9" s="5" t="n">
-        <v>28</v>
-      </c>
       <c r="J9" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -7153,31 +7628,41 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>鸡尾酒裙 Cocktail</t>
+          <t>婚纱 Bride(来图定制)</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="D10" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>1.5</v>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>14</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J10" s="5" t="n">
         <v>2</v>
@@ -7191,20 +7676,20 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>花童裙 Flower Girl</t>
+          <t>伴娘裙 Bridesmaid</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
@@ -7212,10 +7697,10 @@
         </is>
       </c>
       <c r="H11" s="5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J11" s="5" t="n">
         <v>2</v>
@@ -7224,63 +7709,69 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>2026-10 批</t>
+          <t>2026-09 批</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>妈妈装 Mother of the Bride</t>
+          <t>鸡尾酒裙 Cocktail</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>120</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>3</v>
+        <v>20</v>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>2026-10 批</t>
+          <t>2026-09 批</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>晚礼服 Evening</t>
+          <t>花童裙 Flower Girl</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
@@ -7288,10 +7779,10 @@
         </is>
       </c>
       <c r="H13" s="5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J13" s="5" t="n">
         <v>2</v>
@@ -7305,20 +7796,20 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>婚纱 Bride</t>
+          <t>妈妈装 Mother of the Bride</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>40</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
@@ -7326,10 +7817,10 @@
         </is>
       </c>
       <c r="H14" s="5" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J14" s="5" t="n">
         <v>3</v>
@@ -7343,7 +7834,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>伴娘裙 Bridesmaid</t>
+          <t>晚礼服 Evening</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
@@ -7381,34 +7872,34 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>鸡尾酒裙 Cocktail</t>
+          <t>婚纱 Bride(选款)</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>20</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J16" s="5" t="n">
         <v>3</v>
-      </c>
-      <c r="I16" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="J16" s="5" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -7419,31 +7910,41 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>花童裙 Flower Girl</t>
+          <t>婚纱 Bride(来图定制)</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="D17" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>1.5</v>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="I17" s="5" t="n">
-        <v>14</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J17" s="5" t="n">
         <v>2</v>
@@ -7457,20 +7958,20 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>小伴娘裙 JBD</t>
+          <t>伴娘裙 Bridesmaid</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
@@ -7478,10 +7979,10 @@
         </is>
       </c>
       <c r="H18" s="5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J18" s="5" t="n">
         <v>2</v>
@@ -7490,63 +7991,63 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>2026-11 批</t>
+          <t>2026-10 批</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>妈妈装 Mother of the Bride</t>
+          <t>鸡尾酒裙 Cocktail</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>150</v>
+        <v>15</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>2026-11 批</t>
+          <t>2026-10 批</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>晚礼服 Evening</t>
+          <t>花童裙 Flower Girl</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
@@ -7554,10 +8055,10 @@
         </is>
       </c>
       <c r="H20" s="5" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="J20" s="5" t="n">
         <v>2</v>
@@ -7566,39 +8067,45 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>2026-11 批</t>
+          <t>2026-10 批</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>婚纱 Bride</t>
+          <t>小伴娘裙 JBD</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>1.5</v>
+        <v>30</v>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -7609,34 +8116,34 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>伴娘裙 Bridesmaid</t>
+          <t>妈妈装 Mother of the Bride</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>40</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -7647,20 +8154,20 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>舞会裙 Prom</t>
+          <t>晚礼服 Evening</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
@@ -7668,10 +8175,10 @@
         </is>
       </c>
       <c r="H23" s="5" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="J23" s="5" t="n">
         <v>2</v>
@@ -7685,7 +8192,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>鸡尾酒裙 Cocktail</t>
+          <t>婚纱 Bride(选款)</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
@@ -7702,17 +8209,17 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -7723,31 +8230,41 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>花童裙 Flower Girl</t>
+          <t>婚纱 Bride(来图定制)</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E25" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="F25" s="5" t="n">
-        <v>0.8</v>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="I25" s="5" t="n">
-        <v>7</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J25" s="5" t="n">
         <v>2</v>
@@ -7756,63 +8273,63 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>2026-12 批</t>
+          <t>2026-11 批</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>妈妈装 Mother of the Bride</t>
+          <t>伴娘裙 Bridesmaid</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="E26" s="5" t="n">
         <v>40</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>2026-12 批</t>
+          <t>2026-11 批</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>晚礼服 Evening</t>
+          <t>舞会裙 Prom</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
@@ -7820,10 +8337,10 @@
         </is>
       </c>
       <c r="H27" s="5" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="J27" s="5" t="n">
         <v>2</v>
@@ -7832,36 +8349,36 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>2026-12 批</t>
+          <t>2026-11 批</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>婚纱 Bride</t>
+          <t>鸡尾酒裙 Cocktail</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E28" s="5" t="n">
         <v>20</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
         <v>6</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="J28" s="5" t="n">
         <v>2</v>
@@ -7870,25 +8387,25 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>2026-12 批</t>
+          <t>2026-11 批</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>伴娘裙 Bridesmaid</t>
+          <t>花童裙 Flower Girl</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
@@ -7896,10 +8413,10 @@
         </is>
       </c>
       <c r="H29" s="5" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="J29" s="5" t="n">
         <v>2</v>
@@ -7913,34 +8430,34 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>舞会裙 Prom</t>
+          <t>妈妈装 Mother of the Bride</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="E30" s="5" t="n">
         <v>40</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -7951,20 +8468,20 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>鸡尾酒裙 Cocktail</t>
+          <t>晚礼服 Evening</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
@@ -7972,10 +8489,10 @@
         </is>
       </c>
       <c r="H31" s="5" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="J31" s="5" t="n">
         <v>2</v>
@@ -7989,31 +8506,41 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>花童裙 Flower Girl</t>
+          <t>婚纱 Bride(来图定制)</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="D32" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="E32" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="F32" s="5" t="n">
-        <v>1.5</v>
+        <v>10</v>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="I32" s="5" t="n">
-        <v>14</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J32" s="5" t="n">
         <v>2</v>
@@ -8027,17 +8554,17 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>小伴娘裙 JBD</t>
+          <t>伴娘裙 Bridesmaid</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F33" s="5" t="n">
         <v>1.5</v>
@@ -8048,10 +8575,10 @@
         </is>
       </c>
       <c r="H33" s="5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="J33" s="5" t="n">
         <v>2</v>
@@ -8060,60 +8587,60 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>2027-01 批</t>
+          <t>2026-12 批</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>妈妈装 Mother of the Bride</t>
+          <t>舞会裙 Prom</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="E34" s="5" t="n">
         <v>40</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>2027-01 批</t>
+          <t>2026-12 批</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>晚礼服 Evening</t>
+          <t>鸡尾酒裙 Cocktail</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F35" s="5" t="n">
         <v>1.5</v>
@@ -8124,10 +8651,10 @@
         </is>
       </c>
       <c r="H35" s="5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="J35" s="5" t="n">
         <v>2</v>
@@ -8136,36 +8663,36 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>2027-01 批</t>
+          <t>2026-12 批</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>婚纱 Bride</t>
+          <t>花童裙 Flower Girl</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>20</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
         <v>6</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="J36" s="5" t="n">
         <v>2</v>
@@ -8174,22 +8701,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>2027-01 批</t>
+          <t>2026-12 批</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>伴娘裙 Bridesmaid</t>
+          <t>小伴娘裙 JBD</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F37" s="5" t="n">
         <v>1.5</v>
@@ -8200,10 +8727,10 @@
         </is>
       </c>
       <c r="H37" s="5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="J37" s="5" t="n">
         <v>2</v>
@@ -8217,34 +8744,34 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>舞会裙 Prom</t>
+          <t>妈妈装 Mother of the Bride</t>
         </is>
       </c>
       <c r="C38" s="5" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="E38" s="5" t="n">
         <v>40</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -8255,20 +8782,20 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>鸡尾酒裙 Cocktail</t>
+          <t>晚礼服 Evening</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
@@ -8276,10 +8803,10 @@
         </is>
       </c>
       <c r="H39" s="5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J39" s="5" t="n">
         <v>2</v>
@@ -8293,31 +8820,41 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>花童裙 Flower Girl</t>
+          <t>婚纱 Bride(来图定制)</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="D40" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="E40" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="F40" s="5" t="n">
-        <v>1.5</v>
+        <v>10</v>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="H40" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="I40" s="5" t="n">
-        <v>14</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J40" s="5" t="n">
         <v>2</v>
@@ -8326,63 +8863,63 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>2027-02 批</t>
+          <t>2027-01 批</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>妈妈装 Mother of the Bride</t>
+          <t>伴娘裙 Bridesmaid</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="E41" s="5" t="n">
         <v>40</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>2027-02 批</t>
+          <t>2027-01 批</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>晚礼服 Evening</t>
+          <t>舞会裙 Prom</t>
         </is>
       </c>
       <c r="C42" s="5" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
@@ -8390,10 +8927,10 @@
         </is>
       </c>
       <c r="H42" s="5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J42" s="5" t="n">
         <v>2</v>
@@ -8402,36 +8939,36 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>2027-02 批</t>
+          <t>2027-01 批</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>婚纱 Bride</t>
+          <t>鸡尾酒裙 Cocktail</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="E43" s="5" t="n">
         <v>20</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="J43" s="5" t="n">
         <v>2</v>
@@ -8440,38 +8977,200 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>2027-02 批</t>
+          <t>2027-01 批</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>伴娘裙 Bridesmaid</t>
+          <t>花童裙 Flower Girl</t>
         </is>
       </c>
       <c r="C44" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D44" s="5" t="n">
         <v>30</v>
-      </c>
-      <c r="D44" s="5" t="n">
-        <v>45</v>
       </c>
       <c r="E44" s="5" t="n">
         <v>20</v>
       </c>
       <c r="F44" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="J44" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>2027-02 批</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>妈妈装 Mother of the Bride</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>2027-02 批</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>晚礼服 Evening</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F46" s="5" t="n">
         <v>2.2</v>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="H44" s="5" t="n">
+      <c r="H46" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="I44" s="5" t="n">
+      <c r="I46" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="J44" s="5" t="n">
+      <c r="J46" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>2027-02 批</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>婚纱 Bride(来图定制)</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>2027-02 批</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>伴娘裙 Bridesmaid</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="J48" s="5" t="n">
         <v>2</v>
       </c>
     </row>

--- a/上架准备工作按周排期_2026-08_2027-02.xlsx
+++ b/上架准备工作按周排期_2026-08_2027-02.xlsx
@@ -13,6 +13,7 @@
     <sheet name="批次甘特总览" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="每周工作清单" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="产能与作图拆解" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="作图负荷vs产能" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -47,7 +48,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -94,6 +95,11 @@
         <fgColor rgb="00D9D2E9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -121,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -162,6 +168,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -528,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -650,49 +662,61 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="28" customHeight="1">
+    <row r="12" ht="70" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>作图产能</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>单个制作: 1名设计师1款/天, 即5款/人·周, 共10人, 满投入上限50款/周(设计师另有其他需求, 有调整空间); 批量制作: 约20款/天, 满投入上限100款/周(批量线还承担在架款图片迭代, 可调整)。来图定制款按批量线处理。批次作图量按其作图周期(2-3周)均摊计算每周负荷, 详见"作图负荷vs产能"表。排期保守地要求每批作图在首个上架周前全部完成(留缓冲), 因此每月月初周作图负荷很低; 高负荷周(占用≥80%)可把当月靠后周次上架款的作图顺延到月初空档周削峰。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
           <t>春节安排</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>假设 2027/2/5-2/18 放假14天(以公司通知为准), 2/8周与2/15周不排任何工作。2月120款全部于 1/29(节前)完成作图, 分 2/1周(65款)与 2/22周(55款)两次上架。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>2027-03 批次提示</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>受春节影响, 3月批次(量待定)中妈妈装需提前: 1/18-1/29 完成选款打分定款, 节前完成SPU并启动作图, 节后 2/22周 收尾作图, 3月第1周正常上架; 常规品类节后 2/22周 立即选款(或直接定款); 婚纱可优先用来图定制款过渡。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>2027-03 批次提示</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>受春节影响, 3月批次(量待定)中妈妈装需提前: 1/18-1/29 完成选款打分定款, 节前完成SPU并启动作图, 节后 2/22周 收尾作图, 3月第1周正常上架; 常规品类节后 2/22周 立即选款(或直接定款); 婚纱可优先用来图定制款过渡。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
           <t>8月追赶(当前进度)</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>BD: 选款打分已完成→本周定款; ED: 已定款→本周SPU+作图; MBD: 作图中→8/10周起滚动上架; WD: 未启动→本周直接定款30款(来图定制另覆盖20款), 8/24周起上架, 必要时部分顺延至9月第1周。8月上架量后置明显(8/24、8/31两周合计145款), 属追赶期特殊情况。</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>图例</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>选款=浅蓝, 打分=黄色, 定款=橙色, 生成SPU=浅紫, 作图=蓝紫, 上架=绿色, 春节假期=灰色, 直接定款候选=红色。</t>
         </is>
@@ -9177,4 +9201,1126 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>周次</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>在制批次</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>单个需求(款)</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>需设计师(人, 5款/人·周)</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>设计师占用率(共10人)</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>批量需求(款)</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>批量占用(天, 20款/天)</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>批量占用率(按5天)</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>批量剩余产能(款, 可用于在架款迭代)</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>提示</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>8/3周 (8.3-8.7)</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>妈妈装2608批、晚礼服2608批</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>8/10周 (8.10-8.14)</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>妈妈装2608批、晚礼服2608批、伴娘裙2608批、婚纱2608批-选款、婚纱2608批-来图定制</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>78%</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>8/17周 (8.17-8.21)</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>伴娘裙2608批、婚纱2608批-选款、婚纱2608批-来图定制、妈妈装2609批、婚纱2609批-选款</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>8/24周 (8.24-8.28)</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>婚纱2608批-选款、妈妈装2609批、晚礼服2609批、伴娘裙2609批、婚纱2609批-选款、婚纱2609批-来图定制、花童裙2609批</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>89%</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>单个作图高负荷: 需保证设计师投入, 排开其他需求</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>8/31周 (8.31-9.4)</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>妈妈装2609批、晚礼服2609批、伴娘裙2609批、婚纱2609批-选款、婚纱2609批-来图定制、鸡尾酒裙2609批、花童裙2609批</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>单个作图高负荷: 需保证设计师投入, 排开其他需求</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>9/7周 (9.7-9.11)</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>鸡尾酒裙2609批</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>93</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>9/14周 (9.14-9.18)</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>妈妈装2610批、婚纱2610批-选款</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>13%</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>9/21周 (9.21-9.25)</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>妈妈装2610批、晚礼服2610批、伴娘裙2610批、婚纱2610批-选款、婚纱2610批-来图定制、小伴娘裙2610批</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>9/28周 (9.28-10.2)</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>妈妈装2610批、晚礼服2610批、伴娘裙2610批、婚纱2610批-选款、婚纱2610批-来图定制、鸡尾酒裙2610批、小伴娘裙2610批</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>10/5周 (10.5-10.9)</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>鸡尾酒裙2610批</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>10/12周 (10.12-10.16)</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>妈妈装2611批、婚纱2611批-选款、花童裙2610批</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>10/19周 (10.19-10.23)</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>妈妈装2611批、晚礼服2611批、伴娘裙2611批、婚纱2611批-选款、婚纱2611批-来图定制、花童裙2610批</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>87%</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>72%</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>单个作图高负荷: 需保证设计师投入, 排开其他需求</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>10/26周 (10.26-10.30)</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>妈妈装2611批、晚礼服2611批、伴娘裙2611批、婚纱2611批-选款、婚纱2611批-来图定制、舞会裙2611批</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>87%</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>72%</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>单个作图高负荷: 需保证设计师投入, 排开其他需求</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>11/2周 (11.2-11.6)</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>舞会裙2611批、鸡尾酒裙2611批</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>86</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>11/9周 (11.9-11.13)</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>鸡尾酒裙2611批、花童裙2611批</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>11/16周 (11.16-11.20)</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>妈妈装2612批、花童裙2611批</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>11/23周 (11.23-11.27)</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>妈妈装2612批、晚礼服2612批、伴娘裙2612批、舞会裙2612批、鸡尾酒裙2612批</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>11/30周 (11.30-12.4)</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>妈妈装2612批、晚礼服2612批、伴娘裙2612批、婚纱2612批-来图定制、舞会裙2612批、鸡尾酒裙2612批</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>12/7周 (12.7-12.11)</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>婚纱2612批-来图定制、花童裙2612批</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>88</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>12/14周 (12.14-12.18)</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>妈妈装2701批、小伴娘裙2612批、花童裙2612批</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>12/21周 (12.21-12.25)</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>妈妈装2701批、晚礼服2701批、伴娘裙2701批、婚纱2701批-来图定制、舞会裙2701批、小伴娘裙2612批</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>12/28周 (12.28-1.1)</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>妈妈装2701批、晚礼服2701批、伴娘裙2701批、婚纱2701批-来图定制、舞会裙2701批、鸡尾酒裙2701批</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>1/4周 (1.4-1.8)</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>鸡尾酒裙2701批</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>1/11周 (1.11-1.15)</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>妈妈装2702批、花童裙2701批</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>26%</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>86.3</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>1/18周 (1.18-1.22)</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>妈妈装2702批、晚礼服2702批、伴娘裙2702批、婚纱2702批-来图定制、花童裙2701批</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>1/25周 (1.25-1.29)</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>妈妈装2702批、晚礼服2702批、伴娘裙2702批、婚纱2702批-来图定制</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>2/8周 (2.8-2.12)</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>春节假期</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="8" t="n"/>
+      <c r="E28" s="8" t="n"/>
+      <c r="F28" s="8" t="n"/>
+      <c r="G28" s="8" t="n"/>
+      <c r="H28" s="8" t="n"/>
+      <c r="I28" s="8" t="n"/>
+      <c r="J28" s="16" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>2/15周 (2.15-2.19)</t>
+        </is>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>春节假期</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="n"/>
+      <c r="D29" s="8" t="n"/>
+      <c r="E29" s="8" t="n"/>
+      <c r="F29" s="8" t="n"/>
+      <c r="G29" s="8" t="n"/>
+      <c r="H29" s="8" t="n"/>
+      <c r="I29" s="8" t="n"/>
+      <c r="J29" s="16" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/上架准备工作按周排期_2026-08_2027-02.xlsx
+++ b/上架准备工作按周排期_2026-08_2027-02.xlsx
@@ -48,7 +48,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -100,6 +100,11 @@
         <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF9999"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -127,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -170,6 +175,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -670,7 +678,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>单个制作: 1名设计师1款/天, 即5款/人·周, 共10人, 满投入上限50款/周(设计师另有其他需求, 有调整空间); 批量制作: 约20款/天, 满投入上限100款/周(批量线还承担在架款图片迭代, 可调整)。来图定制款按批量线处理。批次作图量按其作图周期(2-3周)均摊计算每周负荷, 详见"作图负荷vs产能"表。排期保守地要求每批作图在首个上架周前全部完成(留缓冲), 因此每月月初周作图负荷很低; 高负荷周(占用≥80%)可把当月靠后周次上架款的作图顺延到月初空档周削峰。</t>
+          <t>单个制作: 1名设计师2款/天, 即10款/人·周, 共10人, 理论上限100款/周; 但目前实际分配给新款的量约30款/周(设计师另有其他需求, 有调整空间)。批量制作: 约20款/天, 满投入上限100款/周(批量线还承担在架款图片迭代, 可调整)。来图定制款按批量线处理。批次作图量按其作图周期(2-3周)均摊计算每周负荷, 详见"作图负荷vs产能"表: 超过当前投放30款/周的周需提前与设计团队协调加量。排期保守地要求每批作图在首个上架周前全部完成(留缓冲), 因此每月月初周作图负荷很低; 高负荷周可把当月靠后周次上架款的作图顺延到月初空档周削峰。</t>
         </is>
       </c>
     </row>
@@ -9209,7 +9217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9217,11 +9225,12 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="44" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9242,35 +9251,40 @@
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>需设计师(人, 5款/人·周)</t>
+          <t>需设计师(人, 10款/人·周)</t>
         </is>
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
-          <t>设计师占用率(共10人)</t>
+          <t>占理论产能(100款/周)</t>
         </is>
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
+          <t>对比当前投放(30款/周)</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
           <t>批量需求(款)</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>批量占用(天, 20款/天)</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>批量占用率(按5天)</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>批量剩余产能(款, 可用于在架款迭代)</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>提示</t>
         </is>
@@ -9291,28 +9305,33 @@
         <v>27</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>5.4</v>
+        <v>2.7</v>
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>54%</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="n">
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="F2" s="15" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="G2" s="5" t="n">
+      <c r="H2" s="5" t="n">
         <v>1.4</v>
       </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="I2" s="5" t="n">
+      <c r="J2" s="5" t="n">
         <v>72</v>
       </c>
-      <c r="J2" s="3" t="inlineStr"/>
+      <c r="K2" s="3" t="inlineStr"/>
     </row>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -9329,28 +9348,37 @@
         <v>39</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>7.8</v>
+        <v>3.9</v>
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>78%</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="n">
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>130%</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="n">
         <v>56</v>
       </c>
-      <c r="G3" s="5" t="n">
+      <c r="H3" s="5" t="n">
         <v>2.8</v>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>56%</t>
         </is>
       </c>
-      <c r="I3" s="5" t="n">
+      <c r="J3" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>超当前投放量: 该周新款单个作图需提量至约40款</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -9367,28 +9395,37 @@
         <v>34</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>6.8</v>
+        <v>3.4</v>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>68%</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="n">
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>113%</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="n">
         <v>42.7</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="H4" s="5" t="n">
         <v>2.1</v>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>43%</t>
         </is>
       </c>
-      <c r="I4" s="5" t="n">
+      <c r="J4" s="5" t="n">
         <v>57.3</v>
       </c>
-      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>超当前投放量: 该周新款单个作图需提量至约35款</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -9405,30 +9442,35 @@
         <v>44.5</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="E5" s="15" t="inlineStr">
-        <is>
-          <t>89%</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>148%</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="n">
         <v>67.2</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="H5" s="5" t="n">
         <v>3.4</v>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="J5" s="5" t="n">
         <v>32.8</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>单个作图高负荷: 需保证设计师投入, 排开其他需求</t>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>超当前投放量: 该周新款单个作图需提量至约45款</t>
         </is>
       </c>
     </row>
@@ -9447,30 +9489,35 @@
         <v>41.5</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="E6" s="15" t="inlineStr">
-        <is>
-          <t>83%</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>138%</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="n">
         <v>70.2</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="H6" s="5" t="n">
         <v>3.5</v>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="J6" s="5" t="n">
         <v>29.8</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>单个作图高负荷: 需保证设计师投入, 排开其他需求</t>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>超当前投放量: 该周新款单个作图需提量至约45款</t>
         </is>
       </c>
     </row>
@@ -9489,28 +9536,33 @@
         <v>3</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>6%</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="n">
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="H7" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
-      <c r="I7" s="5" t="n">
+      <c r="J7" s="5" t="n">
         <v>93</v>
       </c>
-      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr"/>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -9527,28 +9579,33 @@
         <v>20</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>40%</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="n">
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="n">
         <v>13.3</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="H8" s="5" t="n">
         <v>0.7</v>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>13%</t>
         </is>
       </c>
-      <c r="I8" s="5" t="n">
+      <c r="J8" s="5" t="n">
         <v>86.7</v>
       </c>
-      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
     </row>
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -9565,28 +9622,37 @@
         <v>36.5</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>7.3</v>
+        <v>3.6</v>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>73%</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="n">
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>122%</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="n">
         <v>61.8</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="H9" s="5" t="n">
         <v>3.1</v>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
       </c>
-      <c r="I9" s="5" t="n">
+      <c r="J9" s="5" t="n">
         <v>38.2</v>
       </c>
-      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>超当前投放量: 该周新款单个作图需提量至约40款</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -9603,28 +9669,37 @@
         <v>38</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>7.6</v>
+        <v>3.8</v>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>76%</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="n">
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>127%</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="n">
         <v>65.3</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="H10" s="5" t="n">
         <v>3.3</v>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
       </c>
-      <c r="I10" s="5" t="n">
+      <c r="J10" s="5" t="n">
         <v>34.7</v>
       </c>
-      <c r="J10" s="3" t="inlineStr"/>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>超当前投放量: 该周新款单个作图需提量至约40款</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
@@ -9641,28 +9716,33 @@
         <v>1.5</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="n">
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="n">
         <v>3.5</v>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="H11" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="I11" s="5" t="n">
+      <c r="J11" s="5" t="n">
         <v>96.5</v>
       </c>
-      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr"/>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -9679,28 +9759,33 @@
         <v>27</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>5.4</v>
+        <v>2.7</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>54%</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="n">
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="H12" s="5" t="n">
         <v>1.2</v>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
       </c>
-      <c r="I12" s="5" t="n">
+      <c r="J12" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="J12" s="3" t="inlineStr"/>
+      <c r="K12" s="3" t="inlineStr"/>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -9717,30 +9802,35 @@
         <v>43.5</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="E13" s="15" t="inlineStr">
-        <is>
-          <t>87%</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>145%</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="n">
         <v>71.5</v>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="H13" s="5" t="n">
         <v>3.6</v>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>72%</t>
         </is>
       </c>
-      <c r="I13" s="5" t="n">
+      <c r="J13" s="5" t="n">
         <v>28.5</v>
       </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>单个作图高负荷: 需保证设计师投入, 排开其他需求</t>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>超当前投放量: 该周新款单个作图需提量至约45款</t>
         </is>
       </c>
     </row>
@@ -9759,30 +9849,35 @@
         <v>43.5</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="E14" s="15" t="inlineStr">
-        <is>
-          <t>87%</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>145%</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="n">
         <v>71.5</v>
       </c>
-      <c r="G14" s="5" t="n">
+      <c r="H14" s="5" t="n">
         <v>3.6</v>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>72%</t>
         </is>
       </c>
-      <c r="I14" s="5" t="n">
+      <c r="J14" s="5" t="n">
         <v>28.5</v>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>单个作图高负荷: 需保证设计师投入, 排开其他需求</t>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>超当前投放量: 该周新款单个作图需提量至约45款</t>
         </is>
       </c>
     </row>
@@ -9801,28 +9896,33 @@
         <v>6</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="n">
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="H15" s="5" t="n">
         <v>0.7</v>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>14%</t>
         </is>
       </c>
-      <c r="I15" s="5" t="n">
+      <c r="J15" s="5" t="n">
         <v>86</v>
       </c>
-      <c r="J15" s="3" t="inlineStr"/>
+      <c r="K15" s="3" t="inlineStr"/>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -9839,28 +9939,33 @@
         <v>4.5</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>9%</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="n">
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="n">
         <v>10.5</v>
       </c>
-      <c r="G16" s="5" t="n">
+      <c r="H16" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="I16" s="5" t="n">
+      <c r="J16" s="5" t="n">
         <v>89.5</v>
       </c>
-      <c r="J16" s="3" t="inlineStr"/>
+      <c r="K16" s="3" t="inlineStr"/>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
@@ -9877,28 +9982,33 @@
         <v>17.5</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>35%</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="n">
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="n">
         <v>14.2</v>
       </c>
-      <c r="G17" s="5" t="n">
+      <c r="H17" s="5" t="n">
         <v>0.7</v>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>14%</t>
         </is>
       </c>
-      <c r="I17" s="5" t="n">
+      <c r="J17" s="5" t="n">
         <v>85.8</v>
       </c>
-      <c r="J17" s="3" t="inlineStr"/>
+      <c r="K17" s="3" t="inlineStr"/>
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -9915,28 +10025,37 @@
         <v>38.5</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>7.7</v>
+        <v>3.9</v>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>77%</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="n">
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="F18" s="16" t="inlineStr">
+        <is>
+          <t>128%</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="n">
         <v>63.2</v>
       </c>
-      <c r="G18" s="5" t="n">
+      <c r="H18" s="5" t="n">
         <v>3.2</v>
       </c>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>63%</t>
         </is>
       </c>
-      <c r="I18" s="5" t="n">
+      <c r="J18" s="5" t="n">
         <v>36.8</v>
       </c>
-      <c r="J18" s="3" t="inlineStr"/>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>超当前投放量: 该周新款单个作图需提量至约40款</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
@@ -9953,28 +10072,37 @@
         <v>38.5</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>7.7</v>
+        <v>3.9</v>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>77%</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="n">
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t>128%</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="n">
         <v>68.2</v>
       </c>
-      <c r="G19" s="5" t="n">
+      <c r="H19" s="5" t="n">
         <v>3.4</v>
       </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>68%</t>
         </is>
       </c>
-      <c r="I19" s="5" t="n">
+      <c r="J19" s="5" t="n">
         <v>31.8</v>
       </c>
-      <c r="J19" s="3" t="inlineStr"/>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>超当前投放量: 该周新款单个作图需提量至约40款</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -9991,28 +10119,33 @@
         <v>3</v>
       </c>
       <c r="D20" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H20" s="5" t="n">
         <v>0.6</v>
       </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>6%</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H20" s="7" t="inlineStr">
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
       </c>
-      <c r="I20" s="5" t="n">
+      <c r="J20" s="5" t="n">
         <v>88</v>
       </c>
-      <c r="J20" s="3" t="inlineStr"/>
+      <c r="K20" s="3" t="inlineStr"/>
     </row>
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
@@ -10029,28 +10162,33 @@
         <v>22</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>44%</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="n">
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="n">
         <v>24.7</v>
       </c>
-      <c r="G21" s="5" t="n">
+      <c r="H21" s="5" t="n">
         <v>1.2</v>
       </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="I21" s="5" t="n">
+      <c r="J21" s="5" t="n">
         <v>75.3</v>
       </c>
-      <c r="J21" s="3" t="inlineStr"/>
+      <c r="K21" s="3" t="inlineStr"/>
     </row>
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -10067,28 +10205,37 @@
         <v>37</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>7.4</v>
+        <v>3.7</v>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>74%</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="n">
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>123%</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="n">
         <v>64.7</v>
       </c>
-      <c r="G22" s="5" t="n">
+      <c r="H22" s="5" t="n">
         <v>3.2</v>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
       </c>
-      <c r="I22" s="5" t="n">
+      <c r="J22" s="5" t="n">
         <v>35.3</v>
       </c>
-      <c r="J22" s="3" t="inlineStr"/>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>超当前投放量: 该周新款单个作图需提量至约40款</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="28" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
@@ -10105,28 +10252,37 @@
         <v>38.5</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>7.7</v>
+        <v>3.9</v>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>77%</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="n">
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
+        <is>
+          <t>128%</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="n">
         <v>68.2</v>
       </c>
-      <c r="G23" s="5" t="n">
+      <c r="H23" s="5" t="n">
         <v>3.4</v>
       </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="I23" s="7" t="inlineStr">
         <is>
           <t>68%</t>
         </is>
       </c>
-      <c r="I23" s="5" t="n">
+      <c r="J23" s="5" t="n">
         <v>31.8</v>
       </c>
-      <c r="J23" s="3" t="inlineStr"/>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>超当前投放量: 该周新款单个作图需提量至约40款</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -10143,28 +10299,33 @@
         <v>4.5</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>9%</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="n">
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="n">
         <v>10.5</v>
       </c>
-      <c r="G24" s="5" t="n">
+      <c r="H24" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="H24" s="7" t="inlineStr">
+      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="I24" s="5" t="n">
+      <c r="J24" s="5" t="n">
         <v>89.5</v>
       </c>
-      <c r="J24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="inlineStr"/>
     </row>
     <row r="25" ht="28" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
@@ -10181,28 +10342,33 @@
         <v>13</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>26%</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="n">
+          <t>13%</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="n">
         <v>13.7</v>
       </c>
-      <c r="G25" s="5" t="n">
+      <c r="H25" s="5" t="n">
         <v>0.7</v>
       </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>14%</t>
         </is>
       </c>
-      <c r="I25" s="5" t="n">
+      <c r="J25" s="5" t="n">
         <v>86.3</v>
       </c>
-      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
     </row>
     <row r="26" ht="28" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -10219,28 +10385,33 @@
         <v>22</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>44%</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="n">
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="n">
         <v>39.7</v>
       </c>
-      <c r="G26" s="5" t="n">
+      <c r="H26" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H26" s="7" t="inlineStr">
+      <c r="I26" s="7" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="I26" s="5" t="n">
+      <c r="J26" s="5" t="n">
         <v>60.3</v>
       </c>
-      <c r="J26" s="3" t="inlineStr"/>
+      <c r="K26" s="3" t="inlineStr"/>
     </row>
     <row r="27" ht="28" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
@@ -10257,36 +10428,41 @@
         <v>19</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>38%</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="n">
+          <t>19%</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="n">
         <v>32.7</v>
       </c>
-      <c r="G27" s="5" t="n">
+      <c r="H27" s="5" t="n">
         <v>1.6</v>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="I27" s="7" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
       </c>
-      <c r="I27" s="5" t="n">
+      <c r="J27" s="5" t="n">
         <v>67.3</v>
       </c>
-      <c r="J27" s="3" t="inlineStr"/>
+      <c r="K27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="16" t="inlineStr">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>2/8周 (2.8-2.12)</t>
         </is>
       </c>
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
         <is>
           <t>春节假期</t>
         </is>
@@ -10298,15 +10474,16 @@
       <c r="G28" s="8" t="n"/>
       <c r="H28" s="8" t="n"/>
       <c r="I28" s="8" t="n"/>
-      <c r="J28" s="16" t="n"/>
+      <c r="J28" s="17" t="n"/>
+      <c r="K28" s="8" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="inlineStr">
+      <c r="A29" s="17" t="inlineStr">
         <is>
           <t>2/15周 (2.15-2.19)</t>
         </is>
       </c>
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B29" s="17" t="inlineStr">
         <is>
           <t>春节假期</t>
         </is>
@@ -10318,7 +10495,8 @@
       <c r="G29" s="8" t="n"/>
       <c r="H29" s="8" t="n"/>
       <c r="I29" s="8" t="n"/>
-      <c r="J29" s="16" t="n"/>
+      <c r="J29" s="17" t="n"/>
+      <c r="K29" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/上架准备工作按周排期_2026-08_2027-02.xlsx
+++ b/上架准备工作按周排期_2026-08_2027-02.xlsx
@@ -14,6 +14,7 @@
     <sheet name="每周工作清单" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="产能与作图拆解" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="作图负荷vs产能" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="单个作图投放计划" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -548,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -682,49 +683,61 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="28" customHeight="1">
+    <row r="13" ht="56" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>单个作图投放计划</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>"作图负荷vs产能"表是按保守窗口(每批图在首个上架周前完成)计算的需求基线, 呈月中下旬高、月初低的锯齿; "单个作图投放计划"表将其平滑: 在"每款的图须在其上架周前一周的周五完成、SPU生成后才进作图队列、春节两周不排工"的约束下, 按最早截止优先排产, 得到恒定25款/周的最小可行投放量(2/1周13款收尾)。25是数学下限、无缓冲, 建议实际投放维持当前30款/周: 按25的计划表执行, 每周富余约5款用于吸收延误或在架款优化; 2月起的空档周可提前投放3月批次。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
           <t>春节安排</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>假设 2027/2/5-2/18 放假14天(以公司通知为准), 2/8周与2/15周不排任何工作。2月120款全部于 1/29(节前)完成作图, 分 2/1周(65款)与 2/22周(55款)两次上架。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="42" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>2027-03 批次提示</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>受春节影响, 3月批次(量待定)中妈妈装需提前: 1/18-1/29 完成选款打分定款, 节前完成SPU并启动作图, 节后 2/22周 收尾作图, 3月第1周正常上架; 常规品类节后 2/22周 立即选款(或直接定款); 婚纱可优先用来图定制款过渡。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>2027-03 批次提示</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>受春节影响, 3月批次(量待定)中妈妈装需提前: 1/18-1/29 完成选款打分定款, 节前完成SPU并启动作图, 节后 2/22周 收尾作图, 3月第1周正常上架; 常规品类节后 2/22周 立即选款(或直接定款); 婚纱可优先用来图定制款过渡。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
           <t>8月追赶(当前进度)</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>BD: 选款打分已完成→本周定款; ED: 已定款→本周SPU+作图; MBD: 作图中→8/10周起滚动上架; WD: 未启动→本周直接定款30款(来图定制另覆盖20款), 8/24周起上架, 必要时部分顺延至9月第1周。8月上架量后置明显(8/24、8/31两周合计145款), 属追赶期特殊情况。</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>图例</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>选款=浅蓝, 打分=黄色, 定款=橙色, 生成SPU=浅紫, 作图=蓝紫, 上架=绿色, 春节假期=灰色, 直接定款候选=红色。</t>
         </is>
@@ -10501,4 +10514,844 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>周次</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>建议投放量(款)</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>批次明细</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>对比当前投放(30款/周)</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>占理论产能(100款/周)</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>8/3周 (8.3-8.7)</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>妈妈装2608批 24、晚礼服2608批 1</t>
+        </is>
+      </c>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>8/10周 (8.10-8.14)</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>晚礼服2608批 8、妈妈装2608批 11、伴娘裙2608批 6</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>8/17周 (8.17-8.21)</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>妈妈装2608批 7、晚礼服2608批 3、伴娘裙2608批 6、婚纱2608批 9</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>8/24周 (8.24-8.28)</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>婚纱2608批 9、妈妈装2609批 12、婚纱2609批 4</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>8/31周 (8.31-9.4)</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>婚纱2609批 2.5、晚礼服2609批 3、伴娘裙2609批 3、花童裙2609批 4.5、妈妈装2609批 12</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>9/7周 (9.7-9.11)</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>婚纱2609批 3.1、晚礼服2609批 3、伴娘裙2609批 3、鸡尾酒裙2609批 6、妈妈装2609批 9.9</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>9/14周 (9.14-9.18)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>妈妈装2609批 10.3、婚纱2609批 4.2、晚礼服2609批 3、伴娘裙2609批 3、花童裙2609批 4.5</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>9/21周 (9.21-9.25)</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>妈妈装2609批 3.8、婚纱2609批 4.2、晚礼服2609批 3、伴娘裙2609批 3、妈妈装2610批 11</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>9/28周 (9.28-10.2)</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>妈妈装2610批 11.5、婚纱2610批 3、晚礼服2610批 3、伴娘裙2610批 3、小伴娘裙2610批 4.5</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>10/5周 (10.5-10.9)</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>妈妈装2610批 13、婚纱2610批 3、晚礼服2610批 3、伴娘裙2610批 3、鸡尾酒裙2610批 3</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>10/12周 (10.12-10.16)</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>妈妈装2610批 11.5、婚纱2610批 3、晚礼服2610批 3、伴娘裙2610批 3、小伴娘裙2610批 4.5</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>10/19周 (10.19-10.23)</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>妈妈装2610批 1、婚纱2610批 3、晚礼服2610批 3、伴娘裙2610批 3、花童裙2610批 6、妈妈装2611批 9</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>10/26周 (10.26-10.30)</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>妈妈装2611批 15、婚纱2611批 3.4、晚礼服2611批 3.6、伴娘裙2611批 3</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>11/2周 (11.2-11.6)</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>婚纱2611批 1.4、晚礼服2611批 3.6、伴娘裙2611批 3、舞会裙2611批 6、妈妈装2611批 11</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>11/9周 (11.9-11.13)</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>妈妈装2611批 10、婚纱2611批 2.4、晚礼服2611批 3.6、伴娘裙2611批 3、鸡尾酒裙2611批 6</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>11/16周 (11.16-11.20)</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>妈妈装2611批 13、婚纱2611批 2.4、晚礼服2611批 3.6、伴娘裙2611批 3、花童裙2611批 3</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>11/23周 (11.23-11.27)</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>妈妈装2611批 2、婚纱2611批 2.4、晚礼服2611批 3.6、伴娘裙2611批 3、妈妈装2612批 12、舞会裙2612批 2</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>11/30周 (11.30-12.4)</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>舞会裙2612批 1、晚礼服2612批 3.9、伴娘裙2612批 3、鸡尾酒裙2612批 6、妈妈装2612批 11.1</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>12/7周 (12.7-12.11)</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>妈妈装2612批 12.9、舞会裙2612批 5.2、晚礼服2612批 3.9、伴娘裙2612批 3</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>12/14周 (12.14-12.18)</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>舞会裙2612批 0.8、晚礼服2612批 3.6、伴娘裙2612批 3、花童裙2612批 6、妈妈装2612批 11.6</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>12/21周 (12.21-12.25)</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>妈妈装2612批 0.4、舞会裙2612批 3、晚礼服2612批 3.6、伴娘裙2612批 3、小伴娘裙2612批 6、妈妈装2701批 9</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>12/28周 (12.28-1.1)</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>妈妈装2701批 15、舞会裙2701批 4、晚礼服2701批 3、伴娘裙2701批 3</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>1/4周 (1.4-1.8)</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>舞会裙2701批 2.5、晚礼服2701批 3、伴娘裙2701批 3、鸡尾酒裙2701批 4.5、妈妈装2701批 12</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>1/11周 (1.11-1.15)</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>舞会裙2701批 2.5、晚礼服2701批 3、伴娘裙2701批 3、鸡尾酒裙2701批 4.5、妈妈装2701批 12</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>1/18周 (1.18-1.22)</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>舞会裙2701批 3、晚礼服2701批 3、伴娘裙2701批 3、花童裙2701批 6、妈妈装2702批 10</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>1/25周 (1.25-1.29)</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>妈妈装2702批 16、晚礼服2702批 4.5、伴娘裙2702批 4.5</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2/1周 (2.1-2.5)</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>妈妈装2702批 4、晚礼服2702批 4.5、伴娘裙2702批 4.5</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>13%</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2/8周 (2.8-2.12)</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>春节假期</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="n"/>
+      <c r="D29" s="8" t="n"/>
+      <c r="E29" s="8" t="n"/>
+      <c r="F29" s="17" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2/15周 (2.15-2.19)</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>春节假期</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="n"/>
+      <c r="D30" s="8" t="n"/>
+      <c r="E30" s="8" t="n"/>
+      <c r="F30" s="17" t="n"/>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2/22周 (2.22-2.26)</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="3" t="inlineStr"/>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>空档: 可提前投放3月批次作图</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>3/1周 (3.1-3.5)</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="3" t="inlineStr"/>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>空档: 可提前投放3月批次作图</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/上架准备工作按周排期_2026-08_2027-02.xlsx
+++ b/上架准备工作按周排期_2026-08_2027-02.xlsx
@@ -49,7 +49,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -101,11 +101,6 @@
         <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9999"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -133,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -176,9 +171,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -679,7 +671,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>单个制作: 1名设计师2款/天, 即10款/人·周, 共10人, 理论上限100款/周; 但目前实际分配给新款的量约30款/周(设计师另有其他需求, 有调整空间)。批量制作: 约20款/天, 满投入上限100款/周(批量线还承担在架款图片迭代, 可调整)。来图定制款按批量线处理。批次作图量按其作图周期(2-3周)均摊计算每周负荷, 详见"作图负荷vs产能"表: 超过当前投放30款/周的周需提前与设计团队协调加量。排期保守地要求每批作图在首个上架周前全部完成(留缓冲), 因此每月月初周作图负荷很低; 高负荷周可把当月靠后周次上架款的作图顺延到月初空档周削峰。</t>
+          <t>单个制作: 1名设计师2款/天, 即10款/人·周, 共10人, 理论上限100款/周; 但目前实际分配给新款的量约30款/周(设计师另有其他需求, 有调整空间)。批量制作: 约20款/天, 满投入上限100款/周(批量线还承担在架款图片迭代, 可调整)。来图定制款按批量线处理。"作图负荷vs产能"表同时展示两个口径: 基线需求(保守窗口: 每批图压在首个上架周前完成, 呈月中下旬高的锯齿)与平滑后投放(SPU完成即进作图队列、按截止时间排产, 恒定25款/周); 占用率按平滑后口径计算。</t>
         </is>
       </c>
     </row>
@@ -9230,20 +9222,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="44" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="44" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9259,45 +9252,50 @@
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>单个需求(款)</t>
+          <t>单个基线需求(款, 图压上架前完成)</t>
         </is>
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>需设计师(人, 10款/人·周)</t>
+          <t>单个平滑后投放(款, 见投放计划表)</t>
         </is>
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
-          <t>占理论产能(100款/周)</t>
+          <t>需设计师(人, 10款/人·周, 按平滑)</t>
         </is>
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
-          <t>对比当前投放(30款/周)</t>
+          <t>占理论产能(100款/周, 按平滑)</t>
         </is>
       </c>
       <c r="G1" s="4" t="inlineStr">
         <is>
+          <t>对比当前投放(30款/周, 按平滑)</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
           <t>批量需求(款)</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>批量占用(天, 20款/天)</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>批量占用率(按5天)</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>批量剩余产能(款, 可用于在架款迭代)</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>提示</t>
         </is>
@@ -9318,33 +9316,36 @@
         <v>27</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E2" s="7" t="inlineStr">
-        <is>
-          <t>27%</t>
-        </is>
-      </c>
-      <c r="F2" s="15" t="inlineStr">
-        <is>
-          <t>90%</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G2" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="H2" s="5" t="n">
+      <c r="I2" s="5" t="n">
         <v>1.4</v>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="J2" s="5" t="n">
+      <c r="K2" s="5" t="n">
         <v>72</v>
       </c>
-      <c r="K2" s="3" t="inlineStr"/>
+      <c r="L2" s="3" t="inlineStr"/>
     </row>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -9361,35 +9362,38 @@
         <v>39</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>39%</t>
-        </is>
-      </c>
-      <c r="F3" s="16" t="inlineStr">
-        <is>
-          <t>130%</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G3" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="n">
         <v>56</v>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="I3" s="5" t="n">
         <v>2.8</v>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>56%</t>
         </is>
       </c>
-      <c r="J3" s="5" t="n">
+      <c r="K3" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>超当前投放量: 该周新款单个作图需提量至约40款</t>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>基线需求39款, 已通过提前开工平滑至25款</t>
         </is>
       </c>
     </row>
@@ -9408,35 +9412,38 @@
         <v>34</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>34%</t>
-        </is>
-      </c>
-      <c r="F4" s="16" t="inlineStr">
-        <is>
-          <t>113%</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G4" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n">
         <v>42.7</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="I4" s="5" t="n">
         <v>2.1</v>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>43%</t>
         </is>
       </c>
-      <c r="J4" s="5" t="n">
+      <c r="K4" s="5" t="n">
         <v>57.3</v>
       </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>超当前投放量: 该周新款单个作图需提量至约35款</t>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>基线需求34款, 已通过提前开工平滑至25款</t>
         </is>
       </c>
     </row>
@@ -9455,35 +9462,38 @@
         <v>44.5</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>44%</t>
-        </is>
-      </c>
-      <c r="F5" s="16" t="inlineStr">
-        <is>
-          <t>148%</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n">
         <v>67.2</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="I5" s="5" t="n">
         <v>3.4</v>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
       </c>
-      <c r="J5" s="5" t="n">
+      <c r="K5" s="5" t="n">
         <v>32.8</v>
       </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>超当前投放量: 该周新款单个作图需提量至约45款</t>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>基线需求44款, 已通过提前开工平滑至25款</t>
         </is>
       </c>
     </row>
@@ -9502,35 +9512,38 @@
         <v>41.5</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>42%</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>138%</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n">
         <v>70.2</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="I6" s="5" t="n">
         <v>3.5</v>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
       </c>
-      <c r="J6" s="5" t="n">
+      <c r="K6" s="5" t="n">
         <v>29.8</v>
       </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>超当前投放量: 该周新款单个作图需提量至约45款</t>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>基线需求42款, 已通过提前开工平滑至25款</t>
         </is>
       </c>
     </row>
@@ -9549,33 +9562,36 @@
         <v>3</v>
       </c>
       <c r="D7" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="I7" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
-      <c r="J7" s="5" t="n">
+      <c r="K7" s="5" t="n">
         <v>93</v>
       </c>
-      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr"/>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -9592,33 +9608,36 @@
         <v>20</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>2.5</v>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="n">
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n">
         <v>13.3</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="I8" s="5" t="n">
         <v>0.7</v>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>13%</t>
         </is>
       </c>
-      <c r="J8" s="5" t="n">
+      <c r="K8" s="5" t="n">
         <v>86.7</v>
       </c>
-      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
     </row>
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -9635,35 +9654,38 @@
         <v>36.5</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>36%</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>122%</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G9" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n">
         <v>61.8</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="I9" s="5" t="n">
         <v>3.1</v>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
       </c>
-      <c r="J9" s="5" t="n">
+      <c r="K9" s="5" t="n">
         <v>38.2</v>
       </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>超当前投放量: 该周新款单个作图需提量至约40款</t>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>基线需求36款, 已通过提前开工平滑至25款</t>
         </is>
       </c>
     </row>
@@ -9682,35 +9704,38 @@
         <v>38</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>38%</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>127%</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G10" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n">
         <v>65.3</v>
       </c>
-      <c r="H10" s="5" t="n">
+      <c r="I10" s="5" t="n">
         <v>3.3</v>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
       </c>
-      <c r="J10" s="5" t="n">
+      <c r="K10" s="5" t="n">
         <v>34.7</v>
       </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>超当前投放量: 该周新款单个作图需提量至约40款</t>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>基线需求38款, 已通过提前开工平滑至25款</t>
         </is>
       </c>
     </row>
@@ -9729,33 +9754,36 @@
         <v>1.5</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>2.5</v>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="n">
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="n">
         <v>3.5</v>
       </c>
-      <c r="H11" s="5" t="n">
+      <c r="I11" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="J11" s="5" t="n">
+      <c r="K11" s="5" t="n">
         <v>96.5</v>
       </c>
-      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="inlineStr"/>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -9772,33 +9800,36 @@
         <v>27</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>27%</t>
-        </is>
-      </c>
-      <c r="F12" s="15" t="inlineStr">
-        <is>
-          <t>90%</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G12" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="H12" s="5" t="n">
+      <c r="I12" s="5" t="n">
         <v>1.2</v>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
       </c>
-      <c r="J12" s="5" t="n">
+      <c r="K12" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="K12" s="3" t="inlineStr"/>
+      <c r="L12" s="3" t="inlineStr"/>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -9815,35 +9846,38 @@
         <v>43.5</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>44%</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>145%</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G13" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="n">
         <v>71.5</v>
       </c>
-      <c r="H13" s="5" t="n">
+      <c r="I13" s="5" t="n">
         <v>3.6</v>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>72%</t>
         </is>
       </c>
-      <c r="J13" s="5" t="n">
+      <c r="K13" s="5" t="n">
         <v>28.5</v>
       </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>超当前投放量: 该周新款单个作图需提量至约45款</t>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>基线需求44款, 已通过提前开工平滑至25款</t>
         </is>
       </c>
     </row>
@@ -9862,35 +9896,38 @@
         <v>43.5</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>44%</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>145%</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G14" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="n">
         <v>71.5</v>
       </c>
-      <c r="H14" s="5" t="n">
+      <c r="I14" s="5" t="n">
         <v>3.6</v>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>72%</t>
         </is>
       </c>
-      <c r="J14" s="5" t="n">
+      <c r="K14" s="5" t="n">
         <v>28.5</v>
       </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>超当前投放量: 该周新款单个作图需提量至约45款</t>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>基线需求44款, 已通过提前开工平滑至25款</t>
         </is>
       </c>
     </row>
@@ -9909,33 +9946,36 @@
         <v>6</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>6%</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>2.5</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="n">
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G15" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="H15" s="5" t="n">
+      <c r="I15" s="5" t="n">
         <v>0.7</v>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>14%</t>
         </is>
       </c>
-      <c r="J15" s="5" t="n">
+      <c r="K15" s="5" t="n">
         <v>86</v>
       </c>
-      <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="inlineStr"/>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -9952,33 +9992,36 @@
         <v>4.5</v>
       </c>
       <c r="D16" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G16" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I16" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>15%</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="H16" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="J16" s="5" t="n">
+      <c r="K16" s="5" t="n">
         <v>89.5</v>
       </c>
-      <c r="K16" s="3" t="inlineStr"/>
+      <c r="L16" s="3" t="inlineStr"/>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
@@ -9995,33 +10038,36 @@
         <v>17.5</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>18%</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>2.5</v>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>58%</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="n">
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G17" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="n">
         <v>14.2</v>
       </c>
-      <c r="H17" s="5" t="n">
+      <c r="I17" s="5" t="n">
         <v>0.7</v>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>14%</t>
         </is>
       </c>
-      <c r="J17" s="5" t="n">
+      <c r="K17" s="5" t="n">
         <v>85.8</v>
       </c>
-      <c r="K17" s="3" t="inlineStr"/>
+      <c r="L17" s="3" t="inlineStr"/>
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -10038,35 +10084,38 @@
         <v>38.5</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>38%</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>128%</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G18" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="n">
         <v>63.2</v>
       </c>
-      <c r="H18" s="5" t="n">
+      <c r="I18" s="5" t="n">
         <v>3.2</v>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>63%</t>
         </is>
       </c>
-      <c r="J18" s="5" t="n">
+      <c r="K18" s="5" t="n">
         <v>36.8</v>
       </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>超当前投放量: 该周新款单个作图需提量至约40款</t>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>基线需求38款, 已通过提前开工平滑至25款</t>
         </is>
       </c>
     </row>
@@ -10085,35 +10134,38 @@
         <v>38.5</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>38%</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>128%</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G19" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="n">
         <v>68.2</v>
       </c>
-      <c r="H19" s="5" t="n">
+      <c r="I19" s="5" t="n">
         <v>3.4</v>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>68%</t>
         </is>
       </c>
-      <c r="J19" s="5" t="n">
+      <c r="K19" s="5" t="n">
         <v>31.8</v>
       </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>超当前投放量: 该周新款单个作图需提量至约40款</t>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>基线需求38款, 已通过提前开工平滑至25款</t>
         </is>
       </c>
     </row>
@@ -10132,33 +10184,36 @@
         <v>3</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>2.5</v>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="n">
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G20" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="H20" s="5" t="n">
+      <c r="I20" s="5" t="n">
         <v>0.6</v>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
       </c>
-      <c r="J20" s="5" t="n">
+      <c r="K20" s="5" t="n">
         <v>88</v>
       </c>
-      <c r="K20" s="3" t="inlineStr"/>
+      <c r="L20" s="3" t="inlineStr"/>
     </row>
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
@@ -10175,33 +10230,36 @@
         <v>22</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>22%</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>2.5</v>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>73%</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="n">
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G21" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="n">
         <v>24.7</v>
       </c>
-      <c r="H21" s="5" t="n">
+      <c r="I21" s="5" t="n">
         <v>1.2</v>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="J21" s="5" t="n">
+      <c r="K21" s="5" t="n">
         <v>75.3</v>
       </c>
-      <c r="K21" s="3" t="inlineStr"/>
+      <c r="L21" s="3" t="inlineStr"/>
     </row>
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -10218,35 +10276,38 @@
         <v>37</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>37%</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>123%</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G22" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="n">
         <v>64.7</v>
       </c>
-      <c r="H22" s="5" t="n">
+      <c r="I22" s="5" t="n">
         <v>3.2</v>
       </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
       </c>
-      <c r="J22" s="5" t="n">
+      <c r="K22" s="5" t="n">
         <v>35.3</v>
       </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>超当前投放量: 该周新款单个作图需提量至约40款</t>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>基线需求37款, 已通过提前开工平滑至25款</t>
         </is>
       </c>
     </row>
@@ -10265,35 +10326,38 @@
         <v>38.5</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>38%</t>
-        </is>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>128%</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G23" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="n">
         <v>68.2</v>
       </c>
-      <c r="H23" s="5" t="n">
+      <c r="I23" s="5" t="n">
         <v>3.4</v>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>68%</t>
         </is>
       </c>
-      <c r="J23" s="5" t="n">
+      <c r="K23" s="5" t="n">
         <v>31.8</v>
       </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>超当前投放量: 该周新款单个作图需提量至约40款</t>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>基线需求38款, 已通过提前开工平滑至25款</t>
         </is>
       </c>
     </row>
@@ -10312,33 +10376,36 @@
         <v>4.5</v>
       </c>
       <c r="D24" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G24" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I24" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>15%</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="H24" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="J24" s="7" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="J24" s="5" t="n">
+      <c r="K24" s="5" t="n">
         <v>89.5</v>
       </c>
-      <c r="K24" s="3" t="inlineStr"/>
+      <c r="L24" s="3" t="inlineStr"/>
     </row>
     <row r="25" ht="28" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
@@ -10355,33 +10422,36 @@
         <v>13</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>13%</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>2.5</v>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>43%</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="n">
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G25" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="n">
         <v>13.7</v>
       </c>
-      <c r="H25" s="5" t="n">
+      <c r="I25" s="5" t="n">
         <v>0.7</v>
       </c>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="J25" s="7" t="inlineStr">
         <is>
           <t>14%</t>
         </is>
       </c>
-      <c r="J25" s="5" t="n">
+      <c r="K25" s="5" t="n">
         <v>86.3</v>
       </c>
-      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
     </row>
     <row r="26" ht="28" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -10398,33 +10468,36 @@
         <v>22</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>22%</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>2.5</v>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>73%</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="n">
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G26" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="n">
         <v>39.7</v>
       </c>
-      <c r="H26" s="5" t="n">
+      <c r="I26" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="J26" s="7" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="J26" s="5" t="n">
+      <c r="K26" s="5" t="n">
         <v>60.3</v>
       </c>
-      <c r="K26" s="3" t="inlineStr"/>
+      <c r="L26" s="3" t="inlineStr"/>
     </row>
     <row r="27" ht="28" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
@@ -10441,62 +10514,86 @@
         <v>19</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>19%</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>2.5</v>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>63%</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="n">
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G27" s="15" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="n">
         <v>32.7</v>
       </c>
-      <c r="H27" s="5" t="n">
+      <c r="I27" s="5" t="n">
         <v>1.6</v>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="J27" s="7" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
       </c>
-      <c r="J27" s="5" t="n">
+      <c r="K27" s="5" t="n">
         <v>67.3</v>
       </c>
-      <c r="K27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="17" t="inlineStr">
+      <c r="L27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2/1周 (2.1-2.5)</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>13%</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="L28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>2/8周 (2.8-2.12)</t>
         </is>
       </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>春节假期</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="n"/>
-      <c r="E28" s="8" t="n"/>
-      <c r="F28" s="8" t="n"/>
-      <c r="G28" s="8" t="n"/>
-      <c r="H28" s="8" t="n"/>
-      <c r="I28" s="8" t="n"/>
-      <c r="J28" s="17" t="n"/>
-      <c r="K28" s="8" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="17" t="inlineStr">
-        <is>
-          <t>2/15周 (2.15-2.19)</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>春节假期</t>
         </is>
@@ -10508,8 +10605,31 @@
       <c r="G29" s="8" t="n"/>
       <c r="H29" s="8" t="n"/>
       <c r="I29" s="8" t="n"/>
-      <c r="J29" s="17" t="n"/>
+      <c r="J29" s="16" t="n"/>
       <c r="K29" s="8" t="n"/>
+      <c r="L29" s="8" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>2/15周 (2.15-2.19)</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>春节假期</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8" t="n"/>
+      <c r="E30" s="8" t="n"/>
+      <c r="F30" s="8" t="n"/>
+      <c r="G30" s="8" t="n"/>
+      <c r="H30" s="8" t="n"/>
+      <c r="I30" s="8" t="n"/>
+      <c r="J30" s="16" t="n"/>
+      <c r="K30" s="8" t="n"/>
+      <c r="L30" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11278,10 +11398,10 @@
           <t>春节假期</t>
         </is>
       </c>
-      <c r="C29" s="17" t="n"/>
+      <c r="C29" s="16" t="n"/>
       <c r="D29" s="8" t="n"/>
       <c r="E29" s="8" t="n"/>
-      <c r="F29" s="17" t="n"/>
+      <c r="F29" s="16" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -11294,10 +11414,10 @@
           <t>春节假期</t>
         </is>
       </c>
-      <c r="C30" s="17" t="n"/>
+      <c r="C30" s="16" t="n"/>
       <c r="D30" s="8" t="n"/>
       <c r="E30" s="8" t="n"/>
-      <c r="F30" s="17" t="n"/>
+      <c r="F30" s="16" t="n"/>
     </row>
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="2" t="inlineStr">

--- a/上架准备工作按周排期_2026-08_2027-02.xlsx
+++ b/上架准备工作按周排期_2026-08_2027-02.xlsx
@@ -675,7 +675,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="70" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>单个作图投放计划</t>
@@ -683,7 +683,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>"作图负荷vs产能"表是按保守窗口(每批图在首个上架周前完成)计算的需求基线, 呈月中下旬高、月初低的锯齿; "单个作图投放计划"表将其平滑: 在"每款的图须在其上架周前一周的周五完成、SPU生成后才进作图队列、春节两周不排工"的约束下, 按最早截止优先排产, 得到恒定25款/周的最小可行投放量(2/1周13款收尾)。25是数学下限、无缓冲, 建议实际投放维持当前30款/周: 按25的计划表执行, 每周富余约5款用于吸收延误或在架款优化; 2月起的空档周可提前投放3月批次。</t>
+          <t>"单个作图投放计划"表给出平滑后的每周排产明细: 在"每款的图须在其上架周前一周的周五完成、SPU生成后才进作图队列、春节两周不排工"的约束下, 按最早截止优先排产, 得到恒定25款/周的最小可行投放量(2/1周13款收尾)。注意: 甘特总览与每周工作清单中的"作图"窗口是最晚完成基线, 单个作图的实际开工与排量以本投放计划表为准(SPU完成即可提前开工)。25是数学下限、无缓冲, 建议实际投放维持当前30款/周: 按25的计划表执行, 每周富余约5款用于吸收延误或在架款优化; 2月起的空档周可提前投放3月批次。</t>
         </is>
       </c>
     </row>
@@ -7519,14 +7519,20 @@
       <c r="C6" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="D6" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>1.5</v>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
@@ -10605,9 +10611,9 @@
       <c r="G29" s="8" t="n"/>
       <c r="H29" s="8" t="n"/>
       <c r="I29" s="8" t="n"/>
-      <c r="J29" s="16" t="n"/>
+      <c r="J29" s="8" t="n"/>
       <c r="K29" s="8" t="n"/>
-      <c r="L29" s="8" t="n"/>
+      <c r="L29" s="16" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="16" t="inlineStr">
@@ -10627,9 +10633,9 @@
       <c r="G30" s="8" t="n"/>
       <c r="H30" s="8" t="n"/>
       <c r="I30" s="8" t="n"/>
-      <c r="J30" s="16" t="n"/>
+      <c r="J30" s="8" t="n"/>
       <c r="K30" s="8" t="n"/>
-      <c r="L30" s="8" t="n"/>
+      <c r="L30" s="16" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
